--- a/src/paper_list.xlsx
+++ b/src/paper_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yizhang/Desktop/Data Agents Survey/awesome-data-agents/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA90024C-810F-0C4C-AEB6-68438FBFB490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C2120C-ACD4-7547-98D6-275804B92079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="46080" windowHeight="25420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="46080" windowHeight="25420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="L1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="499">
   <si>
     <r>
       <rPr>
@@ -2652,6 +2652,18 @@
   </si>
   <si>
     <t>https://dl.acm.org/doi/epdf/10.1145/3769771</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeepPrep</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeepPrep: An LLM-Powered Agentic System for Autonomous Data Preparation</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2602.07371</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3561,7 +3573,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3853,10 +3865,16 @@
     <xf numFmtId="0" fontId="13" fillId="46" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="56" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4402,7 +4420,7 @@
       <c r="D11" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="98" t="s">
+      <c r="E11" s="97" t="s">
         <v>495</v>
       </c>
       <c r="F11" s="27" t="s">
@@ -6936,7 +6954,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K255"/>
+  <dimension ref="A1:K256"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -7334,8 +7352,8 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="19" customHeight="1">
-      <c r="A20" s="3"/>
-      <c r="B20" s="16"/>
+      <c r="A20" s="84"/>
+      <c r="B20" s="99"/>
       <c r="C20" s="57" t="s">
         <v>312</v>
       </c>
@@ -7354,58 +7372,61 @@
     </row>
     <row r="21" spans="1:11" ht="19" customHeight="1">
       <c r="A21" s="3"/>
-      <c r="B21" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="C21" s="59" t="s">
-        <v>314</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>315</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="G21" s="35">
-        <v>2024</v>
+      <c r="B21" s="16"/>
+      <c r="C21" s="57" t="s">
+        <v>496</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="E21" s="100" t="s">
+        <v>498</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>434</v>
+      </c>
+      <c r="G21" s="16">
+        <v>2026</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="19" customHeight="1">
       <c r="A22" s="3"/>
-      <c r="B22" s="35"/>
+      <c r="B22" s="35" t="s">
+        <v>183</v>
+      </c>
       <c r="C22" s="59" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>318</v>
+        <v>145</v>
       </c>
       <c r="G22" s="35">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="19" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="35"/>
       <c r="C23" s="59" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G23" s="35">
         <v>2025</v>
@@ -7413,39 +7434,39 @@
     </row>
     <row r="24" spans="1:11" ht="19" customHeight="1">
       <c r="A24" s="3"/>
-      <c r="B24" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C24" s="60" t="s">
-        <v>322</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="G24" s="1">
-        <v>2024</v>
+      <c r="B24" s="35"/>
+      <c r="C24" s="59" t="s">
+        <v>319</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>320</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="G24" s="35">
+        <v>2025</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="19" customHeight="1">
       <c r="A25" s="3"/>
-      <c r="B25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>192</v>
+      </c>
       <c r="C25" s="60" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G25" s="1">
         <v>2024</v>
@@ -7454,43 +7475,39 @@
     <row r="26" spans="1:11" ht="19" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="61" t="s">
-        <v>326</v>
+      <c r="C26" s="60" t="s">
+        <v>324</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="G26" s="1">
         <v>2024</v>
       </c>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
     </row>
     <row r="27" spans="1:11" ht="19" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="60" t="s">
-        <v>328</v>
+      <c r="C27" s="61" t="s">
+        <v>326</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="G27" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H27" s="49"/>
       <c r="I27" s="49"/>
@@ -7500,36 +7517,40 @@
     <row r="28" spans="1:11" ht="19" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="61" t="s">
-        <v>330</v>
+      <c r="C28" s="60" t="s">
+        <v>328</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>332</v>
+        <v>135</v>
       </c>
       <c r="G28" s="1">
         <v>2025</v>
       </c>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="49"/>
     </row>
     <row r="29" spans="1:11" ht="19" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="60" t="s">
-        <v>333</v>
+      <c r="C29" s="61" t="s">
+        <v>330</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>135</v>
+        <v>332</v>
       </c>
       <c r="G29" s="1">
         <v>2025</v>
@@ -7539,13 +7560,13 @@
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="60" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F30" s="48" t="s">
         <v>135</v>
@@ -7555,61 +7576,61 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="19" customHeight="1">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="3"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="19" customHeight="1">
+      <c r="A32" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B32" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="62" t="s">
+      <c r="C32" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D32" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E32" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F31" s="40" t="s">
+      <c r="F32" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G32" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="19" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="62" t="s">
-        <v>339</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="G32" s="7">
-        <v>2024</v>
-      </c>
-    </row>
     <row r="33" spans="1:8" ht="19" customHeight="1">
-      <c r="A33" s="3"/>
+      <c r="A33" s="8"/>
       <c r="B33" s="7"/>
       <c r="C33" s="62" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F33" s="40" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="G33" s="7">
         <v>2024</v>
@@ -7618,153 +7639,153 @@
     <row r="34" spans="1:8" ht="19" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="63" t="s">
-        <v>343</v>
+      <c r="C34" s="62" t="s">
+        <v>341</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="G34" s="7">
         <v>2024</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="19" customHeight="1">
-      <c r="A35" s="84"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="73" t="s">
+      <c r="A35" s="3"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="G35" s="7">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="19" customHeight="1">
+      <c r="A36" s="84"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="73" t="s">
         <v>345</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E36" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F35" s="40" t="s">
+      <c r="F36" s="40" t="s">
         <v>273</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G36" s="7">
         <v>2025</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="19" customHeight="1">
-      <c r="A36" s="3"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="73" t="s">
-        <v>476</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="F36" s="40" t="s">
-        <v>479</v>
-      </c>
-      <c r="G36" s="7">
-        <v>2026</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="19" customHeight="1">
       <c r="A37" s="3"/>
-      <c r="B37" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="C37" s="65" t="s">
-        <v>347</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F37" s="36" t="s">
-        <v>321</v>
-      </c>
-      <c r="G37" s="10">
-        <v>2023</v>
+      <c r="B37" s="7"/>
+      <c r="C37" s="73" t="s">
+        <v>476</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F37" s="40" t="s">
+        <v>479</v>
+      </c>
+      <c r="G37" s="7">
+        <v>2026</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="19" customHeight="1">
       <c r="A38" s="3"/>
-      <c r="B38" s="10"/>
+      <c r="B38" s="10" t="s">
+        <v>222</v>
+      </c>
       <c r="C38" s="65" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>135</v>
+        <v>321</v>
       </c>
       <c r="G38" s="10">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="19" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="10"/>
       <c r="C39" s="65" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="G39" s="10">
         <v>2024</v>
       </c>
-      <c r="H39" s="41"/>
     </row>
     <row r="40" spans="1:8" ht="19" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="10"/>
       <c r="C40" s="65" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>355</v>
+        <v>215</v>
       </c>
       <c r="G40" s="10">
-        <v>2025</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="H40" s="41"/>
     </row>
     <row r="41" spans="1:8" ht="19" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="10"/>
       <c r="C41" s="65" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>138</v>
+        <v>355</v>
       </c>
       <c r="G41" s="10">
         <v>2025</v>
@@ -7773,17 +7794,17 @@
     <row r="42" spans="1:8" ht="19" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="10"/>
-      <c r="C42" s="64" t="s">
-        <v>358</v>
+      <c r="C42" s="65" t="s">
+        <v>356</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>483</v>
+        <v>357</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G42" s="10">
         <v>2025</v>
@@ -7792,14 +7813,14 @@
     <row r="43" spans="1:8" ht="19" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="10"/>
-      <c r="C43" s="65" t="s">
-        <v>359</v>
+      <c r="C43" s="64" t="s">
+        <v>358</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>360</v>
+        <v>483</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="F43" s="36" t="s">
         <v>135</v>
@@ -7810,39 +7831,39 @@
     </row>
     <row r="44" spans="1:8" ht="19" customHeight="1">
       <c r="A44" s="3"/>
-      <c r="B44" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="C44" s="74" t="s">
-        <v>361</v>
-      </c>
-      <c r="D44" s="38" t="s">
-        <v>362</v>
-      </c>
-      <c r="E44" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="F44" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="G44" s="11">
-        <v>2024</v>
+      <c r="B44" s="10"/>
+      <c r="C44" s="65" t="s">
+        <v>359</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="G44" s="10">
+        <v>2025</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="19" customHeight="1">
       <c r="A45" s="3"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="75" t="s">
-        <v>363</v>
+      <c r="B45" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" s="74" t="s">
+        <v>361</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F45" s="39" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
       <c r="G45" s="11">
         <v>2024</v>
@@ -7851,190 +7872,190 @@
     <row r="46" spans="1:8" ht="19" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="11"/>
-      <c r="C46" s="74" t="s">
+      <c r="C46" s="75" t="s">
+        <v>363</v>
+      </c>
+      <c r="D46" s="38" t="s">
+        <v>364</v>
+      </c>
+      <c r="E46" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="G46" s="11">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="19" customHeight="1">
+      <c r="A47" s="3"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="74" t="s">
         <v>365</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D47" s="38" t="s">
         <v>366</v>
       </c>
-      <c r="E46" s="38" t="s">
+      <c r="E47" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="F46" s="39" t="s">
+      <c r="F47" s="39" t="s">
         <v>273</v>
-      </c>
-      <c r="G46" s="11">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="19" customHeight="1">
-      <c r="A47" s="84"/>
-      <c r="B47" s="95"/>
-      <c r="C47" s="75" t="s">
-        <v>367</v>
-      </c>
-      <c r="D47" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="E47" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="F47" s="39" t="s">
-        <v>238</v>
       </c>
       <c r="G47" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="19" customHeight="1">
-      <c r="A48" s="3"/>
-      <c r="B48" s="11"/>
+      <c r="A48" s="84"/>
+      <c r="B48" s="95"/>
       <c r="C48" s="75" t="s">
+        <v>367</v>
+      </c>
+      <c r="D48" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="E48" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="F48" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="G48" s="11">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="19" customHeight="1">
+      <c r="A49" s="3"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="75" t="s">
         <v>492</v>
       </c>
-      <c r="D48" s="38" t="s">
+      <c r="D49" s="38" t="s">
         <v>493</v>
       </c>
-      <c r="E48" s="96" t="s">
+      <c r="E49" s="96" t="s">
         <v>494</v>
       </c>
-      <c r="F48" s="39" t="s">
+      <c r="F49" s="39" t="s">
         <v>479</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G49" s="11">
         <v>2026</v>
       </c>
-      <c r="H48">
+      <c r="H49">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="19" customHeight="1">
-      <c r="A49" s="3"/>
-      <c r="B49" s="16" t="s">
+    <row r="50" spans="1:8" ht="19" customHeight="1">
+      <c r="A50" s="3"/>
+      <c r="B50" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="C49" s="58" t="s">
+      <c r="C50" s="58" t="s">
         <v>369</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D50" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E50" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F49" s="33" t="s">
+      <c r="F50" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="G49" s="16">
+      <c r="G50" s="16">
         <v>2023</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="19" customHeight="1">
-      <c r="A50" s="3"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="58" t="s">
-        <v>371</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>372</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="F50" s="33" t="s">
-        <v>355</v>
-      </c>
-      <c r="G50" s="16">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="19" customHeight="1">
+    <row r="51" spans="1:8" ht="19" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="16"/>
-      <c r="C51" s="57" t="s">
-        <v>373</v>
+      <c r="C51" s="58" t="s">
+        <v>371</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F51" s="33" t="s">
-        <v>191</v>
+        <v>355</v>
       </c>
       <c r="G51" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="19" customHeight="1">
+    <row r="52" spans="1:8" ht="19" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="16"/>
-      <c r="C52" s="58" t="s">
-        <v>375</v>
+      <c r="C52" s="57" t="s">
+        <v>373</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F52" s="33" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="G52" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="19" customHeight="1">
+    <row r="53" spans="1:8" ht="19" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="16"/>
       <c r="C53" s="58" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="G53" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="19" customHeight="1">
+    <row r="54" spans="1:8" ht="19" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="16"/>
       <c r="C54" s="58" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F54" s="33" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="G54" s="16">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="19" customHeight="1">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="19" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="16"/>
-      <c r="C55" s="57" t="s">
-        <v>381</v>
+      <c r="C55" s="58" t="s">
+        <v>379</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F55" s="33" t="s">
         <v>145</v>
@@ -8043,36 +8064,36 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="19" customHeight="1">
+    <row r="56" spans="1:8" ht="19" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="16"/>
       <c r="C56" s="57" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="G56" s="33">
+        <v>145</v>
+      </c>
+      <c r="G56" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="19" customHeight="1">
+    <row r="57" spans="1:8" ht="19" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="16"/>
       <c r="C57" s="57" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F57" s="33" t="s">
         <v>135</v>
@@ -8081,95 +8102,95 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="19" customHeight="1">
-      <c r="A58" s="42"/>
-      <c r="B58" s="17" t="s">
+    <row r="58" spans="1:8" ht="19" customHeight="1">
+      <c r="A58" s="3"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="57" t="s">
+        <v>385</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="G58" s="33">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="19" customHeight="1">
+      <c r="A59" s="42"/>
+      <c r="B59" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="C58" s="68" t="s">
+      <c r="C59" s="68" t="s">
         <v>387</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D59" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="E58" s="24" t="s">
+      <c r="E59" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F58" s="21" t="s">
+      <c r="F59" s="21" t="s">
         <v>191</v>
-      </c>
-      <c r="G58" s="43">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="19" customHeight="1">
-      <c r="A59" s="42"/>
-      <c r="B59" s="43"/>
-      <c r="C59" s="76" t="s">
-        <v>389</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="E59" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="F59" s="25" t="s">
-        <v>391</v>
       </c>
       <c r="G59" s="43">
         <v>2024</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="14">
+    <row r="60" spans="1:8" ht="19" customHeight="1">
       <c r="A60" s="42"/>
       <c r="B60" s="43"/>
       <c r="C60" s="76" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>262</v>
+        <v>391</v>
       </c>
       <c r="G60" s="43">
         <v>2024</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="19" customHeight="1">
+    <row r="61" spans="1:8" ht="14">
       <c r="A61" s="42"/>
       <c r="B61" s="43"/>
-      <c r="C61" s="68" t="s">
-        <v>394</v>
+      <c r="C61" s="76" t="s">
+        <v>392</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>135</v>
+        <v>262</v>
       </c>
       <c r="G61" s="43">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="19" customHeight="1">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="19" customHeight="1">
       <c r="A62" s="42"/>
       <c r="B62" s="43"/>
       <c r="C62" s="68" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F62" s="25" t="s">
         <v>135</v>
@@ -8178,39 +8199,39 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="14">
+    <row r="63" spans="1:8" ht="19" customHeight="1">
       <c r="A63" s="42"/>
       <c r="B63" s="43"/>
-      <c r="C63" s="76" t="s">
-        <v>398</v>
+      <c r="C63" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>262</v>
+        <v>135</v>
       </c>
       <c r="G63" s="43">
         <v>2025</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="14">
+    <row r="64" spans="1:8" ht="14">
       <c r="A64" s="42"/>
       <c r="B64" s="43"/>
       <c r="C64" s="76" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="G64" s="43">
         <v>2025</v>
@@ -8220,16 +8241,16 @@
       <c r="A65" s="42"/>
       <c r="B65" s="43"/>
       <c r="C65" s="76" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="G65" s="43">
         <v>2025</v>
@@ -8239,38 +8260,48 @@
       <c r="A66" s="42"/>
       <c r="B66" s="43"/>
       <c r="C66" s="76" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="G66" s="43">
         <v>2025</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="17">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="72"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="4"/>
-    </row>
-    <row r="68" spans="1:7">
+    <row r="67" spans="1:7" ht="14">
+      <c r="A67" s="42"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="76" t="s">
+        <v>404</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="E67" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="F67" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="G67" s="43">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="17">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="72"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="45"/>
-      <c r="G68" s="47"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="4"/>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="4"/>
@@ -8312,10 +8343,10 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="72"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="4"/>
+      <c r="D73" s="46"/>
+      <c r="E73" s="46"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="47"/>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="4"/>
@@ -9955,73 +9986,83 @@
       <c r="F255" s="37"/>
       <c r="G255" s="4"/>
     </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="4"/>
+      <c r="B256" s="4"/>
+      <c r="C256" s="72"/>
+      <c r="D256" s="5"/>
+      <c r="E256" s="5"/>
+      <c r="F256" s="37"/>
+      <c r="G256" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E63" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E64" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="E19" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="E60" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="E46" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="E22" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="E24" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="E25" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="E61" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="E47" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="E23" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="E25" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="E26" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
     <hyperlink ref="E14" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="E55" r:id="rId9" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="E27" r:id="rId10" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="E29" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="E51" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="E45" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="E56" r:id="rId9" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="E28" r:id="rId10" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="E30" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="E52" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="E46" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
     <hyperlink ref="E15" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="E61" r:id="rId15" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="E58" r:id="rId16" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="E62" r:id="rId15" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="E59" r:id="rId16" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
     <hyperlink ref="E17" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="E64" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="E52" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="E26" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="E40" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="E44" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="E20" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="E37" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="E5" r:id="rId25" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="E43" r:id="rId26" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="E13" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="E7" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="E4" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="E65" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="E62" r:id="rId31" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="E57" r:id="rId32" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="E33" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="E53" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="E2" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="E16" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="E54" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="E23" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="E30" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="E11" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="E42" r:id="rId41" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="E32" r:id="rId42" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="E18" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="E3" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="E49" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="E12" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="E56" r:id="rId47" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="E8" r:id="rId48" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="E50" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="E41" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="E21" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="E59" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="E34" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="E39" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
-    <hyperlink ref="E38" r:id="rId55" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
-    <hyperlink ref="E31" r:id="rId56" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
-    <hyperlink ref="E66" r:id="rId57" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
-    <hyperlink ref="E28" r:id="rId58" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
-    <hyperlink ref="E35" r:id="rId59" xr:uid="{7EC1841A-D2E4-4D40-85F8-574AF7C9ED0F}"/>
-    <hyperlink ref="E9" r:id="rId60" xr:uid="{5F14C7A6-B6D6-9542-8B33-155349E77E8F}"/>
-    <hyperlink ref="E10" r:id="rId61" xr:uid="{AF98066F-1603-B94A-BA89-552597EAD77F}"/>
-    <hyperlink ref="E6" r:id="rId62" xr:uid="{C9881E59-5194-2E4A-BA83-759370DAD6ED}"/>
-    <hyperlink ref="E47" r:id="rId63" xr:uid="{5BC41198-863A-4B49-A628-ACE02D2FCC04}"/>
-    <hyperlink ref="E48" r:id="rId64" xr:uid="{C7D2FA05-774D-B74F-BB11-AA780E335549}"/>
+    <hyperlink ref="E65" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="E53" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="E27" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="E41" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="E45" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="E38" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="E5" r:id="rId24" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="E44" r:id="rId25" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="E13" r:id="rId26" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="E7" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="E4" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
+    <hyperlink ref="E66" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
+    <hyperlink ref="E63" r:id="rId30" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="E58" r:id="rId31" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="E34" r:id="rId32" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="E54" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="E2" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="E16" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="E55" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="E24" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="E31" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="E11" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
+    <hyperlink ref="E43" r:id="rId40" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="E33" r:id="rId41" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="E18" r:id="rId42" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="E3" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="E50" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="E12" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="E57" r:id="rId46" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="E8" r:id="rId47" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="E51" r:id="rId48" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="E42" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="E22" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="E60" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="E35" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="E40" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
+    <hyperlink ref="E39" r:id="rId54" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
+    <hyperlink ref="E32" r:id="rId55" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
+    <hyperlink ref="E67" r:id="rId56" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
+    <hyperlink ref="E29" r:id="rId57" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
+    <hyperlink ref="E36" r:id="rId58" xr:uid="{7EC1841A-D2E4-4D40-85F8-574AF7C9ED0F}"/>
+    <hyperlink ref="E9" r:id="rId59" xr:uid="{5F14C7A6-B6D6-9542-8B33-155349E77E8F}"/>
+    <hyperlink ref="E10" r:id="rId60" xr:uid="{AF98066F-1603-B94A-BA89-552597EAD77F}"/>
+    <hyperlink ref="E6" r:id="rId61" xr:uid="{C9881E59-5194-2E4A-BA83-759370DAD6ED}"/>
+    <hyperlink ref="E48" r:id="rId62" xr:uid="{5BC41198-863A-4B49-A628-ACE02D2FCC04}"/>
+    <hyperlink ref="E49" r:id="rId63" xr:uid="{C7D2FA05-774D-B74F-BB11-AA780E335549}"/>
+    <hyperlink ref="E20" r:id="rId64" xr:uid="{7830403C-4CB8-1F42-AB6B-8837083A1F83}"/>
+    <hyperlink ref="E21" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10042,36 +10083,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="97" t="s">
+      <c r="C1" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="97" t="s">
+      <c r="D1" s="98" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="97" t="s">
+      <c r="E1" s="98" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="97" t="s">
+      <c r="F1" s="98" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="97" t="s">
+      <c r="G1" s="98" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19" customHeight="1">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
     </row>
     <row r="3" spans="1:7" ht="14">
       <c r="A3" s="37">

--- a/src/paper_list.xlsx
+++ b/src/paper_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yizhang/Desktop/Data Agents Survey/awesome-data-agents/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C2120C-ACD4-7547-98D6-275804B92079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D2A17A-8F5F-DD42-B8A6-2EBBC7723887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="46080" windowHeight="25420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="46080" windowHeight="25420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="L1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="504">
   <si>
     <r>
       <rPr>
@@ -2664,6 +2664,26 @@
   </si>
   <si>
     <t>https://arxiv.org/pdf/2602.07371</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICLR</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZJU</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2509.25084</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scaling Generalist Data-Analytic Agents</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataMind</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3573,7 +3593,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3868,13 +3888,28 @@
     <xf numFmtId="0" fontId="13" fillId="34" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="18" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7353,7 +7388,7 @@
     </row>
     <row r="20" spans="1:11" ht="19" customHeight="1">
       <c r="A20" s="84"/>
-      <c r="B20" s="99"/>
+      <c r="B20" s="98"/>
       <c r="C20" s="57" t="s">
         <v>312</v>
       </c>
@@ -7379,7 +7414,7 @@
       <c r="D21" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="E21" s="100" t="s">
+      <c r="E21" s="99" t="s">
         <v>498</v>
       </c>
       <c r="F21" s="33" t="s">
@@ -10073,7 +10108,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -10083,36 +10118,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="100" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="98" t="s">
+      <c r="B1" s="100" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="98" t="s">
+      <c r="C1" s="100" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="98" t="s">
+      <c r="D1" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="98" t="s">
+      <c r="E1" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="98" t="s">
+      <c r="F1" s="100" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="98" t="s">
+      <c r="G1" s="100" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19" customHeight="1">
-      <c r="A2" s="98"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
     </row>
     <row r="3" spans="1:7" ht="14">
       <c r="A3" s="37">
@@ -10154,24 +10189,24 @@
         <v>412</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14">
-      <c r="A5" s="37">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="77" t="s">
-        <v>413</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>472</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>409</v>
+    <row r="5" spans="1:7" ht="19" customHeight="1">
+      <c r="A5" s="101">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="103" t="s">
+        <v>503</v>
+      </c>
+      <c r="C5" s="104" t="s">
+        <v>502</v>
+      </c>
+      <c r="D5" s="105" t="s">
+        <v>501</v>
+      </c>
+      <c r="E5" s="102" t="s">
+        <v>499</v>
+      </c>
+      <c r="F5" s="104" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14">
@@ -10179,16 +10214,16 @@
         <v>2025</v>
       </c>
       <c r="B6" s="77" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E6" s="37" t="s">
-        <v>417</v>
+        <v>121</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>472</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>409</v>
@@ -10198,145 +10233,157 @@
       <c r="A7" s="37">
         <v>2025</v>
       </c>
-      <c r="B7" s="78" t="s">
-        <v>418</v>
+      <c r="B7" s="77" t="s">
+        <v>415</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="53" t="s">
-        <v>435</v>
-      </c>
-      <c r="F7" s="52" t="s">
-        <v>438</v>
+        <v>120</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14">
       <c r="A8" s="37">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="78" t="s">
+        <v>418</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>435</v>
+      </c>
+      <c r="F8" s="52" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="14">
+      <c r="A9" s="37">
         <v>2024</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B9" s="77" t="s">
         <v>420</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E9" s="53" t="s">
         <v>436</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14">
-      <c r="A9" s="37"/>
-      <c r="B9" s="77" t="s">
-        <v>423</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>433</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="52" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19" customHeight="1">
+    <row r="10" spans="1:7" ht="14">
       <c r="A10" s="37"/>
       <c r="B10" s="77" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C10" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E10" s="37"/>
-      <c r="F10" s="5" t="s">
-        <v>425</v>
+      <c r="F10" s="52" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="19" customHeight="1">
       <c r="A11" s="37"/>
-      <c r="B11" s="78" t="s">
-        <v>126</v>
+      <c r="B11" s="77" t="s">
+        <v>424</v>
       </c>
       <c r="C11" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E11" s="37"/>
       <c r="F11" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="19" customHeight="1">
       <c r="A12" s="37"/>
       <c r="B12" s="78" t="s">
-        <v>427</v>
+        <v>126</v>
       </c>
       <c r="C12" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" s="37"/>
       <c r="F12" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="19" customHeight="1">
       <c r="A13" s="37"/>
-      <c r="B13" s="77" t="s">
-        <v>429</v>
+      <c r="B13" s="78" t="s">
+        <v>427</v>
       </c>
       <c r="C13" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E13" s="37"/>
       <c r="F13" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="19" customHeight="1">
       <c r="A14" s="37"/>
-      <c r="B14" s="78" t="s">
-        <v>431</v>
+      <c r="B14" s="77" t="s">
+        <v>429</v>
       </c>
       <c r="C14" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E14" s="37"/>
       <c r="F14" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="19" customHeight="1">
       <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="B15" s="78" t="s">
+        <v>431</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>433</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="E15" s="37"/>
-      <c r="F15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="19" customHeight="1">
       <c r="A16" s="37"/>
@@ -10346,7 +10393,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="19" customHeight="1">
       <c r="A17" s="37"/>
       <c r="B17" s="37"/>
       <c r="C17" s="5"/>
@@ -11825,6 +11872,14 @@
       <c r="D201" s="5"/>
       <c r="E201" s="37"/>
       <c r="F201" s="5"/>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="37"/>
+      <c r="B202" s="37"/>
+      <c r="C202" s="5"/>
+      <c r="D202" s="5"/>
+      <c r="E202" s="37"/>
+      <c r="F202" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -11840,16 +11895,17 @@
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="D5" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="D8" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="D9" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="D12" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="D14" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="D6" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="D10" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
-    <hyperlink ref="D13" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
-    <hyperlink ref="D7" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="D9" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="D10" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="D13" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="D15" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="D11" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="D12" r:id="rId10" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="D14" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
+    <hyperlink ref="D8" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
+    <hyperlink ref="D5" r:id="rId13" xr:uid="{8F01A46B-F312-6944-B099-6C2A96D521DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/paper_list.xlsx
+++ b/src/paper_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yizhang/Desktop/Data Agents Survey/awesome-data-agents/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D2A17A-8F5F-DD42-B8A6-2EBBC7723887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A962604-B58E-1548-85B9-831CC7515DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="46080" windowHeight="25420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="L1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="515">
   <si>
     <r>
       <rPr>
@@ -2684,6 +2684,44 @@
   </si>
   <si>
     <t>DataMind</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeepEye</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKUST(GZ)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeepEye: A Steerable Self-driving Data Agent System</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/xxxx</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Julis</t>
+  </si>
+  <si>
+    <t>Julius.ai</t>
+  </si>
+  <si>
+    <t>Bayeslab.ai</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bayeslab</t>
+  </si>
+  <si>
+    <t>https://julius.ai/</t>
+  </si>
+  <si>
+    <t>https://bayeslab.ai/</t>
+  </si>
+  <si>
+    <t>SIGMOD Demo</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3593,7 +3631,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3894,9 +3932,6 @@
     <xf numFmtId="0" fontId="13" fillId="18" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3911,6 +3946,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7877,10 +7918,10 @@
         <v>51</v>
       </c>
       <c r="F44" s="36" t="s">
-        <v>135</v>
+        <v>479</v>
       </c>
       <c r="G44" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="19" customHeight="1">
@@ -10108,7 +10149,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:G203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -10118,115 +10159,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="106" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="100" t="s">
+      <c r="C1" s="106" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="100" t="s">
+      <c r="D1" s="106" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="100" t="s">
+      <c r="E1" s="106" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="100" t="s">
+      <c r="F1" s="106" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="100" t="s">
+      <c r="G1" s="106" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19" customHeight="1">
-      <c r="A2" s="100"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-    </row>
-    <row r="3" spans="1:7" ht="14">
+      <c r="A2" s="106"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="37">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B3" s="79" t="s">
-        <v>407</v>
+        <v>504</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>119</v>
+        <v>506</v>
+      </c>
+      <c r="D3" s="105" t="s">
+        <v>507</v>
       </c>
       <c r="E3" s="53" t="s">
-        <v>434</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19" customHeight="1">
+        <v>514</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>505</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="14">
       <c r="A4" s="37">
         <v>2025</v>
       </c>
-      <c r="B4" s="77" t="s">
-        <v>410</v>
+      <c r="B4" s="79" t="s">
+        <v>407</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E4" s="53" t="s">
         <v>434</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19" customHeight="1">
+      <c r="A5" s="37">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="77" t="s">
+        <v>410</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>434</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19" customHeight="1">
-      <c r="A5" s="101">
+    <row r="6" spans="1:7" ht="19" customHeight="1">
+      <c r="A6" s="100">
         <v>2026</v>
       </c>
-      <c r="B5" s="103" t="s">
+      <c r="B6" s="102" t="s">
         <v>503</v>
       </c>
-      <c r="C5" s="104" t="s">
+      <c r="C6" s="103" t="s">
         <v>502</v>
       </c>
-      <c r="D5" s="105" t="s">
+      <c r="D6" s="104" t="s">
         <v>501</v>
       </c>
-      <c r="E5" s="102" t="s">
+      <c r="E6" s="101" t="s">
         <v>499</v>
       </c>
-      <c r="F5" s="104" t="s">
+      <c r="F6" s="103" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="14">
-      <c r="A6" s="37">
-        <v>2025</v>
-      </c>
-      <c r="B6" s="77" t="s">
-        <v>413</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" s="53" t="s">
-        <v>472</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>409</v>
+      <c r="G6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14">
@@ -10234,16 +10281,16 @@
         <v>2025</v>
       </c>
       <c r="B7" s="77" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>417</v>
+        <v>121</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>472</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>409</v>
@@ -10253,163 +10300,197 @@
       <c r="A8" s="37">
         <v>2025</v>
       </c>
-      <c r="B8" s="78" t="s">
-        <v>418</v>
+      <c r="B8" s="77" t="s">
+        <v>415</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>435</v>
-      </c>
-      <c r="F8" s="52" t="s">
-        <v>438</v>
+        <v>120</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14">
       <c r="A9" s="37">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>418</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>435</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14">
+      <c r="A10" s="37">
         <v>2024</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B10" s="77" t="s">
         <v>420</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E10" s="53" t="s">
         <v>436</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14">
-      <c r="A10" s="37"/>
-      <c r="B10" s="77" t="s">
-        <v>423</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>433</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="52" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19" customHeight="1">
+    <row r="11" spans="1:7" ht="14">
       <c r="A11" s="37"/>
       <c r="B11" s="77" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C11" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E11" s="37"/>
-      <c r="F11" s="5" t="s">
-        <v>425</v>
+      <c r="F11" s="52" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="19" customHeight="1">
       <c r="A12" s="37"/>
-      <c r="B12" s="78" t="s">
-        <v>126</v>
+      <c r="B12" s="77" t="s">
+        <v>424</v>
       </c>
       <c r="C12" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E12" s="37"/>
       <c r="F12" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="19" customHeight="1">
       <c r="A13" s="37"/>
       <c r="B13" s="78" t="s">
-        <v>427</v>
+        <v>126</v>
       </c>
       <c r="C13" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E13" s="37"/>
       <c r="F13" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="19" customHeight="1">
       <c r="A14" s="37"/>
-      <c r="B14" s="77" t="s">
-        <v>429</v>
+      <c r="B14" s="78" t="s">
+        <v>427</v>
       </c>
       <c r="C14" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E14" s="37"/>
       <c r="F14" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="19" customHeight="1">
       <c r="A15" s="37"/>
-      <c r="B15" s="78" t="s">
-        <v>431</v>
+      <c r="B15" s="77" t="s">
+        <v>429</v>
       </c>
       <c r="C15" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E15" s="37"/>
       <c r="F15" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="19" customHeight="1">
       <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="B16" s="78" t="s">
+        <v>431</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>433</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="E16" s="37"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" ht="19" customHeight="1">
+      <c r="F16" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19" customHeight="1">
       <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="B17" s="37" t="s">
+        <v>509</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>433</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="E17" s="37"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="F17" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19" customHeight="1">
       <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="B18" s="53" t="s">
+        <v>510</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>433</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>513</v>
+      </c>
       <c r="E18" s="37"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="F18" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="37"/>
       <c r="B19" s="37"/>
       <c r="C19" s="5"/>
@@ -10417,7 +10498,7 @@
       <c r="E19" s="37"/>
       <c r="F19" s="5"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" s="37"/>
       <c r="B20" s="37"/>
       <c r="C20" s="5"/>
@@ -10425,7 +10506,7 @@
       <c r="E20" s="37"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" s="37"/>
       <c r="B21" s="37"/>
       <c r="C21" s="5"/>
@@ -10433,7 +10514,7 @@
       <c r="E21" s="37"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" s="37"/>
       <c r="B22" s="37"/>
       <c r="C22" s="5"/>
@@ -10441,7 +10522,7 @@
       <c r="E22" s="37"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" s="37"/>
       <c r="B23" s="37"/>
       <c r="C23" s="5"/>
@@ -10449,7 +10530,7 @@
       <c r="E23" s="37"/>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24" s="37"/>
       <c r="B24" s="37"/>
       <c r="C24" s="5"/>
@@ -10457,7 +10538,7 @@
       <c r="E24" s="37"/>
       <c r="F24" s="5"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" s="37"/>
       <c r="B25" s="37"/>
       <c r="C25" s="5"/>
@@ -10465,7 +10546,7 @@
       <c r="E25" s="37"/>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" s="37"/>
       <c r="B26" s="37"/>
       <c r="C26" s="5"/>
@@ -10473,7 +10554,7 @@
       <c r="E26" s="37"/>
       <c r="F26" s="5"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" s="37"/>
       <c r="B27" s="37"/>
       <c r="C27" s="5"/>
@@ -10481,7 +10562,7 @@
       <c r="E27" s="37"/>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" s="37"/>
       <c r="B28" s="37"/>
       <c r="C28" s="5"/>
@@ -10489,7 +10570,7 @@
       <c r="E28" s="37"/>
       <c r="F28" s="5"/>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" s="37"/>
       <c r="B29" s="37"/>
       <c r="C29" s="5"/>
@@ -10497,7 +10578,7 @@
       <c r="E29" s="37"/>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30" s="37"/>
       <c r="B30" s="37"/>
       <c r="C30" s="5"/>
@@ -10505,7 +10586,7 @@
       <c r="E30" s="37"/>
       <c r="F30" s="5"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31" s="37"/>
       <c r="B31" s="37"/>
       <c r="C31" s="5"/>
@@ -10513,7 +10594,7 @@
       <c r="E31" s="37"/>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" s="37"/>
       <c r="B32" s="37"/>
       <c r="C32" s="5"/>
@@ -11880,6 +11961,14 @@
       <c r="D202" s="5"/>
       <c r="E202" s="37"/>
       <c r="F202" s="5"/>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="37"/>
+      <c r="B203" s="37"/>
+      <c r="C203" s="5"/>
+      <c r="D203" s="5"/>
+      <c r="E203" s="37"/>
+      <c r="F203" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -11893,19 +11982,20 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="D9" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="D10" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="D13" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="D15" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="D7" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="D11" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="D12" r:id="rId10" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
-    <hyperlink ref="D14" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
-    <hyperlink ref="D8" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
-    <hyperlink ref="D5" r:id="rId13" xr:uid="{8F01A46B-F312-6944-B099-6C2A96D521DA}"/>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="D10" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="D11" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="D14" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="D16" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="D8" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="D12" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="D13" r:id="rId10" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="D15" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
+    <hyperlink ref="D9" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
+    <hyperlink ref="D6" r:id="rId13" xr:uid="{8F01A46B-F312-6944-B099-6C2A96D521DA}"/>
+    <hyperlink ref="D3" r:id="rId14" xr:uid="{4286F07A-CF69-BD44-AA40-BFEEC2472490}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/paper_list.xlsx
+++ b/src/paper_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yizhang/Desktop/Data Agents Survey/awesome-data-agents/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A962604-B58E-1548-85B9-831CC7515DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E613A8FB-20F9-8A47-9B67-860684E9A71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2698,10 +2698,6 @@
     <t>DeepEye: A Steerable Self-driving Data Agent System</t>
   </si>
   <si>
-    <t>https://arxiv.org/abs/xxxx</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Julis</t>
   </si>
   <si>
@@ -2722,6 +2718,10 @@
   </si>
   <si>
     <t>SIGMOD Demo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2603.28889</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -10201,10 +10201,10 @@
         <v>506</v>
       </c>
       <c r="D3" s="105" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="E3" s="53" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F3" s="52" t="s">
         <v>505</v>
@@ -10455,17 +10455,17 @@
     <row r="17" spans="1:7" ht="19" customHeight="1">
       <c r="A17" s="37"/>
       <c r="B17" s="37" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C17" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E17" s="37"/>
       <c r="F17" s="5" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -10474,17 +10474,17 @@
     <row r="18" spans="1:7" ht="19" customHeight="1">
       <c r="A18" s="37"/>
       <c r="B18" s="53" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>433</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G18">
         <v>1</v>

--- a/src/paper_list.xlsx
+++ b/src/paper_list.xlsx
@@ -2,38 +2,522 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yizhang/Desktop/Data Agents Survey/awesome-data-agents/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E613A8FB-20F9-8A47-9B67-860684E9A71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B5EACC-DC80-FB47-A5F5-371B799325DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="46080" windowHeight="25420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="L1" sheetId="2" r:id="rId1"/>
-    <sheet name="L2" sheetId="3" r:id="rId2"/>
-    <sheet name="L3" sheetId="4" r:id="rId3"/>
-    <sheet name="survey" sheetId="5" r:id="rId4"/>
+    <sheet name="L1" sheetId="1" r:id="rId1"/>
+    <sheet name="L2" sheetId="2" r:id="rId2"/>
+    <sheet name="L3" sheetId="3" r:id="rId3"/>
+    <sheet name="survey" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="511">
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Sub-domain</t>
+  </si>
+  <si>
+    <t>Data Agent</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Venue</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Data Management</t>
+  </si>
+  <si>
+    <t>Configuration Tuning</t>
+  </si>
+  <si>
+    <t>LLMTune</t>
+  </si>
+  <si>
+    <t>LLMTune: Accelerate Database Knob Tuning with Large Language Models</t>
+  </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2404.11581v1</t>
+    </r>
+  </si>
+  <si>
+    <t>arXiv</t>
+  </si>
+  <si>
+    <t>λ-Tune</t>
+  </si>
+  <si>
+    <t>λ-Tune: Harnessing Large Language Models for Automated Database System Tuning</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://dl.acm.org/doi/abs/10.1145/3709652</t>
+    </r>
+  </si>
+  <si>
+    <t>SIGMOD</t>
+  </si>
+  <si>
+    <t>LATuner</t>
+  </si>
+  <si>
+    <t>LATuner: An LLM-Enhanced Database Tuning System Based on Adaptive Surrogate Model</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://dl.acm.org/doi/abs/10.1007/978-3-031-70362-1_22</t>
+    </r>
+  </si>
+  <si>
+    <t>ECML PKDD</t>
+  </si>
+  <si>
+    <t>GPTuner</t>
+  </si>
+  <si>
+    <t>GPTuner: A Manual-Reading Database Tuning System via GPT-Guided Bayesian Optimization</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://vldb.org/pvldb/vol17/p1939-tang.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t>VLDB</t>
+  </si>
+  <si>
+    <t>E2ETune</t>
+  </si>
+  <si>
+    <t>E2ETune: End-to-End Knob Tuning via Fine-tuned Generative Language Model</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2404.11581</t>
+    </r>
+  </si>
+  <si>
+    <t>Query Optimization</t>
+  </si>
+  <si>
+    <t>DB-GPT</t>
+  </si>
+  <si>
+    <t>DB-GPT: Large Language Model Meets Database</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://link.springer.com/article/10.1007/s41019-023-00235-6</t>
+    </r>
+  </si>
+  <si>
+    <t>Data Science and Engineering</t>
+  </si>
+  <si>
+    <t>LLM-R2</t>
+  </si>
+  <si>
+    <t>LLM-R2: A Large Language Model Enhanced Rule-Based Rewrite System for Boosting Query Efficiency</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://dl.acm.org/doi/abs/10.14778/3696435.3696440</t>
+    </r>
+  </si>
+  <si>
+    <t>GenRewriter</t>
+  </si>
+  <si>
+    <t>Query Rewriting via Large Language Models</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2403.09060</t>
+    </r>
+  </si>
+  <si>
+    <t>LITHE</t>
+  </si>
+  <si>
+    <t>Query Rewriting via LLMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2502.12918</t>
+    </r>
+  </si>
+  <si>
+    <t>LLM-QO</t>
+  </si>
+  <si>
+    <t>Can Large Language Models Be Query Optimizer for Relational Databases?</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/epdf/10.1145/3769771</t>
+  </si>
+  <si>
+    <t>LLMOpt</t>
+  </si>
+  <si>
+    <t>A Query Optimization Method Utilizing Large Language Models</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2503.06902</t>
+    </r>
+  </si>
+  <si>
+    <t>E3-Rewite</t>
+  </si>
+  <si>
+    <t>E3-Rewrite: Learning to Rewrite SQL for Executability, Equivalence, and Efficiency</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2508.09023</t>
+    </r>
+  </si>
+  <si>
+    <t>System Diagnosis</t>
+  </si>
+  <si>
+    <t>DBG-PT</t>
+  </si>
+  <si>
+    <t>DBG-PT: A Large Language Model Assisted Query Performance Regression Debugger</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://dl.acm.org/doi/abs/10.14778/3685800.3685869</t>
+    </r>
+  </si>
+  <si>
+    <t>Andromeda</t>
+  </si>
+  <si>
+    <t>Automatic Database Configuration Debugging using Retrieval-Augmented Language Models</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://dl.acm.org/doi/abs/10.1145/3709663</t>
+    </r>
+  </si>
+  <si>
+    <t>Data Preparation</t>
+  </si>
+  <si>
+    <t>Data Cleaning</t>
+  </si>
+  <si>
+    <t>FM</t>
+  </si>
+  <si>
+    <t>Can Foundation Models Wrangle Your Data?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2205.09911</t>
+    </r>
+  </si>
+  <si>
+    <t>RetClean</t>
+  </si>
+  <si>
+    <t>RetClean: Retrieval-Based Data Cleaning Using LLMs and Data Lakes</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2303.16909</t>
+    </r>
+  </si>
+  <si>
+    <t>VLDB demo</t>
+  </si>
+  <si>
+    <t>LakeFill</t>
+  </si>
+  <si>
+    <t>Data Imputation with Limited Data Redundancy Using Data Lakes</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://www.vldb.org/pvldb/vol18/p3354-tang.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t>UniDM</t>
+  </si>
+  <si>
+    <t>Unidm: A unified framework for data manipulation with large language models</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/pdf/2405.06510</t>
+    </r>
+  </si>
+  <si>
+    <t>MLSys</t>
+  </si>
+  <si>
+    <t>LLMClean</t>
+  </si>
+  <si>
+    <t>LLMClean: Context-Aware Tabular Data Cleaning via LLM-Generated OFDs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2404.18681</t>
+    </r>
+  </si>
+  <si>
+    <t>ADBIS</t>
+  </si>
+  <si>
+    <t>Data Integration</t>
+  </si>
+  <si>
+    <t>Table-GPT</t>
+  </si>
+  <si>
+    <t>Table-GPT: Table-tuned GPT for Diverse Table Tasks</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/pdf/2310.09263</t>
+    </r>
+  </si>
+  <si>
+    <t>BATCHER</t>
+  </si>
+  <si>
+    <t>Cost-Effective In-Context Learning for Entity Resolution: A Design Space Exploration</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/pdf/2312.03987</t>
+    </r>
+  </si>
+  <si>
+    <t>ICDE</t>
+  </si>
+  <si>
+    <t>Jellyfish</t>
+  </si>
+  <si>
+    <t>Jellyfish: Instruction-Tuning Local Large Language Models for Data Preprocessing</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://aclanthology.org/2024.emnlp-main.497/</t>
+    </r>
+  </si>
+  <si>
+    <t>EMNLP</t>
+  </si>
+  <si>
+    <t>Data Discovery</t>
+  </si>
+  <si>
+    <t>ArcheType</t>
+  </si>
+  <si>
+    <t>ArcheType: A Novel Framework for Open-Source Column Type Annotation using Large Language Models</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/pdf/2310.18208</t>
+    </r>
+  </si>
+  <si>
+    <t>RACOON</t>
+  </si>
+  <si>
+    <t>RACOON: An LLM-based Framework for Retrieval-Augmented Column Type Annotation with a Knowledge Graph</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -42,10 +526,55 @@
     </r>
   </si>
   <si>
+    <t>Cocoon</t>
+  </si>
+  <si>
+    <t>Cocoon: Semantic table profiling using large language model</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://dl.acm.org/doi/abs/10.1145/3665939.3665957</t>
+    </r>
+  </si>
+  <si>
+    <t>HILDA</t>
+  </si>
+  <si>
+    <t>AutoDDG</t>
+  </si>
+  <si>
+    <t>Autoddg: Automated dataset description generation using large language models</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2502.01050</t>
+    </r>
+  </si>
+  <si>
+    <t>Pneuma</t>
+  </si>
+  <si>
+    <t>Pneuma: Leveraging llms for tabular data representation and retrieval in an end-to-end system</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -54,22 +583,34 @@
     </r>
   </si>
   <si>
+    <t>LLMCTA</t>
+  </si>
+  <si>
+    <t>Evaluating Knowledge Generation and Self-refinement Strategies for LLM-Based Column Type Annotation</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2502.01050</t>
+      <t>https://link.springer.com/chapter/10.1007/978-3-032-05281-0_8</t>
     </r>
+  </si>
+  <si>
+    <t>Columbo</t>
+  </si>
+  <si>
+    <t>Columbo: Expanding Abbreviated Column Names for Tabular Data Using Large Language Models</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -78,22 +619,43 @@
     </r>
   </si>
   <si>
+    <t>Data Analysis</t>
+  </si>
+  <si>
+    <t>TableQA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dater </t>
+  </si>
+  <si>
+    <t>Large Language Models are Versatile Decomposers: Decomposing Evidence and Questions for Table-based Reasoning</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://link.springer.com/chapter/10.1007/978-3-032-05281-0_8</t>
+      <t>https://dl.acm.org/doi/10.1145/3539618.3591708</t>
     </r>
+  </si>
+  <si>
+    <t>SIGIR</t>
+  </si>
+  <si>
+    <t>BINDER</t>
+  </si>
+  <si>
+    <t>Binding Language Models in Symbolic Languages</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -102,22 +664,40 @@
     </r>
   </si>
   <si>
+    <t>ICLR</t>
+  </si>
+  <si>
+    <t>Self-augmented Prompting</t>
+  </si>
+  <si>
+    <t>Table Meets LLM: Can Large Language Models Understand Structured Table Data? A Benchmark and Empirical Study</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://dl.acm.org/doi/10.1145/3539618.3591708</t>
+      <t>https://dl.acm.org/doi/abs/10.1145/3616855.3635752</t>
     </r>
+  </si>
+  <si>
+    <t>WSDM</t>
+  </si>
+  <si>
+    <t>TableLlama</t>
+  </si>
+  <si>
+    <t>TableLlama: Towards Open Large Generalist Models for Tables</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -126,22 +706,43 @@
     </r>
   </si>
   <si>
+    <t>NAACL</t>
+  </si>
+  <si>
+    <t>NL2SQL</t>
+  </si>
+  <si>
+    <t>DIN-SQL</t>
+  </si>
+  <si>
+    <t>DIN-SQL: Decomposed In-Context Learning of Text-to-SQL with Self-Correction.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://dl.acm.org/doi/abs/10.1145/3616855.3635752</t>
+      <t>https://arxiv.org/abs/2304.11015</t>
     </r>
+  </si>
+  <si>
+    <t>NeurIPS</t>
+  </si>
+  <si>
+    <t>DAIL-SQL</t>
+  </si>
+  <si>
+    <t>Text-to-SQL Empowered by Large Language Models: A Benchmark Evaluation</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -150,22 +751,34 @@
     </r>
   </si>
   <si>
+    <t>ACT-SQL</t>
+  </si>
+  <si>
+    <t>ACT-SQL: In-Context Learning for Text-to-SQL with Automatically-Generated Chain-of-Thought</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2304.11015</t>
+      <t>https://arxiv.org/pdf/2310.17342</t>
     </r>
+  </si>
+  <si>
+    <t>SuperSQL</t>
+  </si>
+  <si>
+    <t>The Dawn of Natural Language to SQL: Are We Fully Ready?</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -174,22 +787,40 @@
     </r>
   </si>
   <si>
+    <t>NL2VIS</t>
+  </si>
+  <si>
+    <t>Chat2VIS</t>
+  </si>
+  <si>
+    <t>Chat2VIS: Generating Data Visualizations via Natural Language Using ChatGPT, Codex and GPT-3 Large Language Models</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/pdf/2310.17342</t>
+      <t>https://ieeexplore.ieee.org/document/10121440</t>
     </r>
+  </si>
+  <si>
+    <t>IEEE Access</t>
+  </si>
+  <si>
+    <t>NL4DV-LLM</t>
+  </si>
+  <si>
+    <t>Generating Analytic Specifications for Data Visualization from Natural Language Queries using Large Language Models</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -198,22 +829,31 @@
     </r>
   </si>
   <si>
+    <t>VIS</t>
+  </si>
+  <si>
+    <t>Prompt4Vis</t>
+  </si>
+  <si>
+    <t>Prompt4Vis: Prompting Large Language Models with Example Mining for Tabular Data Visualization</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s00778-025-00912-0</t>
+  </si>
+  <si>
+    <t>VLDBJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Step-Text2Vis</t>
+  </si>
+  <si>
+    <t>nvBench 2.0: Resolving Ambiguity in Text-to-Visualization through Stepwise Reasoning</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://ieeexplore.ieee.org/document/10121440</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -222,10 +862,40 @@
     </r>
   </si>
   <si>
+    <t>NeuRIPS</t>
+  </si>
+  <si>
+    <t>Unstructured Data Analysis</t>
+  </si>
+  <si>
+    <t>LongRAG</t>
+  </si>
+  <si>
+    <t>LongRAG: A Dual-Perspective Retrieval-Augmented Generation Paradigm for Long-Context Question Answering</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://aclanthology.org/2024.emnlp-main.1259.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t>RAPTOR</t>
+  </si>
+  <si>
+    <t>RAPTOR: Recursive Abstractive Processing for Tree-Organized Retrieval</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -234,22 +904,34 @@
     </r>
   </si>
   <si>
+    <t>PDFTriage</t>
+  </si>
+  <si>
+    <t>PDFTriage: Question Answering over Long, Structured Documents</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://aclanthology.org/2024.emnlp-main.1259.pdf</t>
+      <t>https://aclanthology.org/2024.emnlp-industry.13.pdf</t>
     </r>
+  </si>
+  <si>
+    <t>DSE</t>
+  </si>
+  <si>
+    <t>Unifying Multimodal Retrieval via Document Screenshot Embedding</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -258,22 +940,34 @@
     </r>
   </si>
   <si>
+    <t>VisDoM</t>
+  </si>
+  <si>
+    <t>VisDoM: Multi-Document QA with Visually Rich Elements Using Multimodal Retrieval-Augmented Generation</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://aclanthology.org/2024.emnlp-industry.13.pdf</t>
+      <t>https://aclanthology.org/2025.naacl-long.310.pdf</t>
     </r>
+  </si>
+  <si>
+    <t>Docopilot</t>
+  </si>
+  <si>
+    <t>Docopilot: Improving Multimodal Models for Document-Level Understanding</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -282,22 +976,40 @@
     </r>
   </si>
   <si>
+    <t>CVPR</t>
+  </si>
+  <si>
+    <t>Report Generation</t>
+  </si>
+  <si>
+    <t>Datatales</t>
+  </si>
+  <si>
+    <t>DataTales: Investigating the use of Large Language Models for Authoring Data-Driven Articles</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://aclanthology.org/2025.naacl-long.310.pdf</t>
+      <t>https://arxiv.org/abs/2308.04076</t>
     </r>
+  </si>
+  <si>
+    <t>Choe et al.</t>
+  </si>
+  <si>
+    <t>Enhancing Data Literacy On-demand: LLMs as Guides for Novices in Chart Interpretation</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -306,22 +1018,40 @@
     </r>
   </si>
   <si>
+    <t>TVCG</t>
+  </si>
+  <si>
+    <t>ReportGPT</t>
+  </si>
+  <si>
+    <t>ReportGPT: Human‑in‑the‑Loop Verifiable Table‑to‑Text Generation</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2308.04076</t>
+      <t>https://aclanthology.org/2024.emnlp-industry.39/</t>
     </r>
+  </si>
+  <si>
+    <t>EMNLP Industry</t>
+  </si>
+  <si>
+    <t>InterChat</t>
+  </si>
+  <si>
+    <t>InterChat: Enhancing Generative Visual Analytics using Multimodal Interactions</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -330,22 +1060,37 @@
     </r>
   </si>
   <si>
+    <t>EuroVis</t>
+  </si>
+  <si>
+    <t>VizTA</t>
+  </si>
+  <si>
+    <t>VizTA: Enhancing Comprehension of Distributional Visualization with Visual-Lexical Fused Conversational Interface</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://aclanthology.org/2024.emnlp-industry.39/</t>
+      <t>https://onlinelibrary.wiley.com/doi/full/10.1111/cgf.70110</t>
     </r>
+  </si>
+  <si>
+    <t>ChartLens</t>
+  </si>
+  <si>
+    <t>ChartLens: Fine-grained Visual Attribution in Charts</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -354,298 +1099,769 @@
     </r>
   </si>
   <si>
+    <t>ACL</t>
+  </si>
+  <si>
+    <t>Li et al.</t>
+  </si>
+  <si>
+    <t>Is Large Language Model Good at Database Knob Tuning? A Comprehensive Experimental Evaluation</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://onlinelibrary.wiley.com/doi/full/10.1111/cgf.70110</t>
+      <t>https://arxiv.org/pdf/2408.02213</t>
     </r>
+  </si>
+  <si>
+    <t>LLMIdxAdvis</t>
+  </si>
+  <si>
+    <t>LLMIdxAdvis: Resource-Efficient Index Advisor Utilizing Large Language Model</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2404.11581v1</t>
+      <t>https://arxiv.org/abs/2503.07884</t>
     </r>
+  </si>
+  <si>
+    <t>RABBIT</t>
+  </si>
+  <si>
+    <t>Rabbit: Retrieval-Augmented Generation Enables Better Automatic Database Knob Tuning</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://dl.acm.org/doi/abs/10.1007/978-3-031-70362-1_22</t>
+      <t>https://ieeexplore.ieee.org/document/11113071</t>
     </r>
+  </si>
+  <si>
+    <t>MCTuner</t>
+  </si>
+  <si>
+    <t>MCTuner: Spatial Decomposition-Enhanced Database Tuning via LLM-Guided Exploration</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://dl.acm.org/doi/abs/10.1145/3709652</t>
+      <t>https://arxiv.org/abs/2509.06298</t>
     </r>
+  </si>
+  <si>
+    <t>AgentTune</t>
+  </si>
+  <si>
+    <t>AgentTune: An Agent-Based Large Language Model Framework for Database Knob Tuning</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3769758</t>
+  </si>
+  <si>
+    <t>SERAG</t>
+  </si>
+  <si>
+    <t>SERAG: Self-Evolving RAG System for Query Optimization</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2404.11581</t>
+      <t>https://viterbi-web.usc.edu/~sabek/pdf/25_workshop_serag.pdf</t>
     </r>
+  </si>
+  <si>
+    <t>SIGMOD Workshop</t>
+  </si>
+  <si>
+    <t>QUITE</t>
+  </si>
+  <si>
+    <t>QUITE: A Query Rewrite System Beyond Rules with LLM Agents</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://vldb.org/pvldb/vol17/p1939-tang.pdf</t>
+      <t>https://arxiv.org/abs/2506.07675</t>
     </r>
+  </si>
+  <si>
+    <t>R-Bot</t>
+  </si>
+  <si>
+    <t>R-Bot: An LLM-Based Query Rewrite System</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://dl.acm.org/doi/abs/10.14778/3696435.3696440</t>
+      <t>https://arxiv.org/abs/2412.01661</t>
     </r>
+  </si>
+  <si>
+    <t>CrackSQL</t>
+  </si>
+  <si>
+    <t>Cracking SQL Barriers: An LLM-based Dialect Translation System</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3725278</t>
+  </si>
+  <si>
+    <t>Panda</t>
+  </si>
+  <si>
+    <t>Panda: Performance Debugging for Databases using LLM Agents</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://link.springer.com/article/10.1007/s41019-023-00235-6</t>
+      <t>https://www.vldb.org/cidrdb/papers/2024/p6-singh.pdf</t>
     </r>
+  </si>
+  <si>
+    <t>CIDR</t>
+  </si>
+  <si>
+    <t>D-Bot</t>
+  </si>
+  <si>
+    <t>D-Bot: Database Diagnosis System using Large Language Models</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2502.12918</t>
+      <t>https://arxiv.org/abs/2312.01454</t>
     </r>
+  </si>
+  <si>
+    <t>DBAIOps</t>
+  </si>
+  <si>
+    <t>DBAIOps: A Reasoning LLM-Enhanced Database Operation and Maintenance System using Knowledge Graphs</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2403.09060</t>
+      <t>https://arxiv.org/abs/2508.01136</t>
     </r>
+  </si>
+  <si>
+    <t>SketchFill</t>
+  </si>
+  <si>
+    <t>SketchFill: Sketch-Guided Code Generation for Imputing Derived Missing Values</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2503.06902</t>
+      <t>https://arxiv.org/abs/2412.19113</t>
     </r>
+  </si>
+  <si>
+    <t>IterClean</t>
+  </si>
+  <si>
+    <t>IterClean: An Iterative Data Cleaning Framework with Large Language Models</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://dl.acm.org/doi/abs/10.14778/3685800.3685869</t>
+      <t>https://dl.acm.org/doi/pdf/10.1145/3674399.3674436</t>
     </r>
+  </si>
+  <si>
+    <t>ACM-TURC</t>
+  </si>
+  <si>
+    <t>AutoPrep</t>
+  </si>
+  <si>
+    <t>AutoPrep: Natural Language Question-Aware Data Preparation with a Multi-Agent Framework</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2508.09023</t>
+      <t>https://arxiv.org/pdf/2412.10422</t>
     </r>
+  </si>
+  <si>
+    <t>AutoDCWorkflow</t>
+  </si>
+  <si>
+    <t>AutoDCWorkflow: LLM-based Data Cleaning Workflow Auto-Generation and Benchmark</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2205.09911</t>
+      <t>https://arxiv.org/abs/2412.06724</t>
     </r>
+  </si>
+  <si>
+    <t>EMNLP Findings</t>
+  </si>
+  <si>
+    <t>CleanAgent</t>
+  </si>
+  <si>
+    <t>CleanAgent: Automating Data Standardization with LLM-based Agents</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://dl.acm.org/doi/abs/10.1145/3709663</t>
+      <t>https://www.vldb.org/2025/Workshops/VLDB-Workshops-2025/DATAI/DATAI25_8.pdf</t>
     </r>
+  </si>
+  <si>
+    <t>VLDB Workshop</t>
+  </si>
+  <si>
+    <t>Bendinelli et al.</t>
+  </si>
+  <si>
+    <t>Exploring LLM Agents for Cleaning Tabular Machine Learning Datasets</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://www.vldb.org/pvldb/vol18/p3354-tang.pdf</t>
+      <t>https://arxiv.org/pdf/2503.06664</t>
     </r>
+  </si>
+  <si>
+    <t>ICLR Workshop</t>
+  </si>
+  <si>
+    <t>MegaTran</t>
+  </si>
+  <si>
+    <t>Weak-to-Strong Prompts with Lightweight-to-Powerful LLMs for High-Accuracy, Low-Cost, and Explainable Data Transformation</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2303.16909</t>
+      <t>https://www.vldb.org/pvldb/vol18/p2371-tang.pdf</t>
     </r>
+  </si>
+  <si>
+    <t>DeepPrep</t>
+  </si>
+  <si>
+    <t>DeepPrep: An LLM-Powered Agentic System for Autonomous Data Preparation</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2602.07371</t>
+  </si>
+  <si>
+    <t>Agent-OM</t>
+  </si>
+  <si>
+    <t>Agent-OM: Leveraging LLM Agents for Ontology Matching</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2404.18681</t>
+      <t>https://arxiv.org/pdf/2312.00326</t>
     </r>
+  </si>
+  <si>
+    <t>MILA</t>
+  </si>
+  <si>
+    <t>Ontology Matching with Large Language Models and Prioritized Depth-First Search</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/pdf/2405.06510</t>
+      <t>https://arxiv.org/pdf/2501.11441</t>
     </r>
+  </si>
+  <si>
+    <t>Information Fusion</t>
+  </si>
+  <si>
+    <t>COMEM</t>
+  </si>
+  <si>
+    <t>Match, Compare, or Select? An Investigation of Large Language Models for Entity Matching</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/pdf/2312.03987</t>
+      <t>https://arxiv.org/pdf/2405.16884</t>
     </r>
+  </si>
+  <si>
+    <t>COLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chorus</t>
+  </si>
+  <si>
+    <t>Chorus: Foundation Models for Unified Data Discovery and Exploration</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/pdf/2310.09263</t>
+      <t>https://dl.acm.org/doi/abs/10.14778/3659437.3659461</t>
     </r>
+  </si>
+  <si>
+    <t>DataVoyager</t>
+  </si>
+  <si>
+    <t>Data-driven Discovery with Large Generative Models</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/pdf/2310.18208</t>
+      <t>https://arxiv.org/pdf/2402.13610</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DATALORE </t>
+  </si>
+  <si>
+    <t>DATALORE: Can a Large Language Model Find All Lost Scrolls in a Data Repository?</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://aclanthology.org/2024.emnlp-main.497/</t>
+      <t>https://ieeexplore.ieee.org/abstract/document/10597732</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> LEDD</t>
+  </si>
+  <si>
+    <t>LEDD: Large Language Model-Empowered Data Discovery in Data Lakes</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://dl.acm.org/doi/abs/10.1145/3665939.3665957</t>
+      <t>https://arxiv.org/abs/2502.15182</t>
     </r>
+  </si>
+  <si>
+    <t>MetaGen</t>
+  </si>
+  <si>
+    <t>Automated Metadata Generation Using Large Language Models: A GPT-4 Case Study for Enterprise Data Profiling</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://sarcouncil.com/download-article/SJECS-221-2025-769-775.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t>Journal for Engineering and Computer Science</t>
+  </si>
+  <si>
+    <t>DBDescGen</t>
+  </si>
+  <si>
+    <t>Automatic database description generation for Text-to-SQL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2502.20657</t>
+    </r>
+  </si>
+  <si>
+    <t>Wang et al.</t>
+  </si>
+  <si>
+    <t>Towards Operationalizing Heterogeneous Data Discovery</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/pdf/2504.02059</t>
+    </r>
+  </si>
+  <si>
+    <t>StructGPT</t>
+  </si>
+  <si>
+    <t>StructGPT: A General Framework for Large Language Model to Reason over Structured Data</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://aclanthology.org/2023.emnlp-main.574/</t>
+    </r>
+  </si>
+  <si>
+    <t>ReAcTable</t>
+  </si>
+  <si>
+    <t>ReAcTable: Enhancing ReAct for Table Question Answering</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://dl.acm.org/doi/10.14778/3659437.3659452</t>
+    </r>
+  </si>
+  <si>
+    <t>CHAIN-OF-TABLE</t>
+  </si>
+  <si>
+    <t>Chain-of-Table: Evolving Tables in the Reasoning Chain for Table Understanding</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2401.04398</t>
+    </r>
+  </si>
+  <si>
+    <t>AutoTQA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AutoTQA: Towards Autonomous Tabular Question Answering through Multi-Agent Large Language Models</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://www.vldb.org/pvldb/vol17/p3920-zhu.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t>Table-Critic</t>
+  </si>
+  <si>
+    <t>Table-Critic: A Multi-Agent Framework for Collaborative Criticism and Refinement in Table Reasoning</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://aclanthology.org/2025.acl-long.853/</t>
+    </r>
+  </si>
+  <si>
+    <t>ST-Raptor</t>
+  </si>
+  <si>
+    <t>ST-Raptor: LLM-Powered Semi-Structured Table Question Answering</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2508.18190</t>
+  </si>
+  <si>
+    <t>MAC-SQL</t>
+  </si>
+  <si>
+    <t>MAC-SQL: A Multi-Agent Collaborative Framework for Text-to-SQL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2312.11242</t>
+    </r>
+  </si>
+  <si>
+    <t>ChatBI</t>
+  </si>
+  <si>
+    <t>Chatbi: Towards natural language to complex business</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/pdf/2405.00527</t>
+    </r>
+  </si>
+  <si>
+    <t>Chase-SQL</t>
+  </si>
+  <si>
+    <t>CHASE-SQL: Multi-Path Reasoning and Preference Optimized Candidate Selection in Text-to-SQL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/abs/2410.01943</t>
+    </r>
+  </si>
+  <si>
+    <t>Alpha-SQL</t>
+  </si>
+  <si>
+    <t>Alpha-SQL: Zero-Shot Text-to-SQL using Monte Carlo Tree Search</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/pdf/2502.17248</t>
+    </r>
+  </si>
+  <si>
+    <t>ICML</t>
+  </si>
+  <si>
+    <t>OpenSearch-SQL</t>
+  </si>
+  <si>
+    <t>OpenSearch-SQL: Enhancing Text-to-SQL with Dynamic Few-shot and Consistency Alignment.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/pdf/2502.14913</t>
+    </r>
+  </si>
+  <si>
+    <t>ReFoRCE</t>
+  </si>
+  <si>
+    <t>ReFoRCE: A Text-to-SQL Agent with Self-Refinement, Consensus Enforcement, and Column Exploration</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://arxiv.org/pdf/2502.00675</t>
+    </r>
+  </si>
+  <si>
+    <t>DeepEye-SQL</t>
+  </si>
+  <si>
+    <t>DeepEye-SQL: A Software-Engineering-Inspired Text-to-SQL Framework</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -654,10 +1870,16 @@
     </r>
   </si>
   <si>
+    <t>MatPlotAgent</t>
+  </si>
+  <si>
+    <t>MatPlotAgent: Method and Evaluation for LLM-Based Agentic Scientific Data Visualization</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -666,10 +1888,16 @@
     </r>
   </si>
   <si>
+    <t>Text2Chart31</t>
+  </si>
+  <si>
+    <t>Text2Chart31: Instruction Tuning for Chart Generation with Automatic Feedback</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -678,10 +1906,16 @@
     </r>
   </si>
   <si>
+    <t>nvAgent</t>
+  </si>
+  <si>
+    <t>NVAGENT: Automated Data Visualization from Natural Language via Collaborative Agent Workflow</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -690,10 +1924,16 @@
     </r>
   </si>
   <si>
+    <t>DeepVIS</t>
+  </si>
+  <si>
+    <t>DeepVIS: Bridging Natural Language and Data Visualization Through Step-wise Reasoning</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -702,10 +1942,25 @@
     </r>
   </si>
   <si>
+    <t>MultiVis-Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multi-Agent Framework with Logic Rules for Reliable and Comprehensive Cross-Modal Data Visualization</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2601.18320</t>
+  </si>
+  <si>
+    <t>FLARE</t>
+  </si>
+  <si>
+    <t>Active Retrieval Augmented Generation</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -714,106 +1969,160 @@
     </r>
   </si>
   <si>
+    <t>ReadAgent</t>
+  </si>
+  <si>
+    <t>A Human-Inspired Reading Agent with Gist Memory of Very Long Contexts</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://dl.acm.org/doi/10.14778/3659437.3659452</t>
+      <t>https://arxiv.org/pdf/2402.09727</t>
     </r>
+  </si>
+  <si>
+    <t>GraphReader</t>
+  </si>
+  <si>
+    <t>GraphReader: Building Graph-based Agent to Enhance Long-Context Abilities of Large Language Models</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2401.04398</t>
+      <t>https://arxiv.org/pdf/2406.14550</t>
     </r>
+  </si>
+  <si>
+    <t>Self-RAG</t>
+  </si>
+  <si>
+    <t>Self-RAG: Learning to Retrieve, Generate, and Critique through Self-Reflection</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://www.vldb.org/pvldb/vol17/p3920-zhu.pdf</t>
+      <t>https://arxiv.org/pdf/2310.11511</t>
     </r>
+  </si>
+  <si>
+    <t>REAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REAR: A Relevance-Aware Retrieval-Augmented Framework for Open-Domain Question Answering </t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://aclanthology.org/2025.acl-long.853/</t>
+      <t>https://aclanthology.org/2024.emnlp-main.321.pdf</t>
     </r>
+  </si>
+  <si>
+    <t>QUEST</t>
+  </si>
+  <si>
+    <t>QUEST: Query Optimization in Unstructured Document Analysis</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2312.11242</t>
+      <t>https://dl.acm.org/doi/pdf/10.14778/3749646.3749713</t>
     </r>
+  </si>
+  <si>
+    <t>Doctopus</t>
+  </si>
+  <si>
+    <t>Doctopus: Budget-aware Structural Table Extraction from Unstructured Documents</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/pdf/2405.00527</t>
+      <t>https://www.vldb.org/pvldb/vol18/p3695-chai.pdf</t>
     </r>
+  </si>
+  <si>
+    <t>MACT</t>
+  </si>
+  <si>
+    <t>Visual Document Understanding and Question Answering: A Multi-Agent Collaboration Framework with Test-Time Scaling</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/abs/2410.01943</t>
+      <t>https://arxiv.org/pdf/2508.03404</t>
     </r>
+  </si>
+  <si>
+    <t>DataPuzzle</t>
+  </si>
+  <si>
+    <t>DataPuzzle: Breaking Free from the Hallucinated Promise of LLMs in Data Analysis</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://arxiv.org/pdf/2502.17248</t>
+      <t>https://arxiv.org/abs/2504.10036</t>
     </r>
+  </si>
+  <si>
+    <t>DataNarrative</t>
+  </si>
+  <si>
+    <t>DataNarrative: Automated Data-Driven Storytelling with Visualizations and Texts</t>
   </si>
   <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -822,10 +2131,16 @@
     </r>
   </si>
   <si>
+    <t>Data Director</t>
+  </si>
+  <si>
+    <t>From Data to Story: Towards Automatic Animated Data Video Creation with LLM-based Multi-Agent Systems</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -834,10 +2149,19 @@
     </r>
   </si>
   <si>
+    <t>VIS  workshop</t>
+  </si>
+  <si>
+    <t>LightVA</t>
+  </si>
+  <si>
+    <t>LightVA: Lightweight Visual Analytics with LLM Agent-Based Task Planning and Execution</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -846,10 +2170,16 @@
     </r>
   </si>
   <si>
+    <t>Multimodal DeepResearcher</t>
+  </si>
+  <si>
+    <t>Multimodal DeepResearcher: Generating Text–Chart Interleaved Reports with an Agentic Framework</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -858,10 +2188,16 @@
     </r>
   </si>
   <si>
+    <t>DAgent</t>
+  </si>
+  <si>
+    <t>DAgent: A Relational Database-Driven Data Analysis Report Generation Agent</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -870,10 +2206,16 @@
     </r>
   </si>
   <si>
+    <t>Chart Insighter</t>
+  </si>
+  <si>
+    <t>ChartInsighter: An Approach for Mitigating Hallucination in Time-Series Chart Summary Generation With a Benchmark Dataset</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -882,10 +2224,16 @@
     </r>
   </si>
   <si>
+    <t>ProactiveVA</t>
+  </si>
+  <si>
+    <t>ProactiveVA: Proactive Visual Analytics with LLM-Based UI Agent</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -894,10 +2242,16 @@
     </r>
   </si>
   <si>
+    <t>VOICE</t>
+  </si>
+  <si>
+    <t>VOICE: Visual Oracle for Interaction, Conversation, and Explanation</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -906,202 +2260,16 @@
     </r>
   </si>
   <si>
+    <t>NLI4VolVis</t>
+  </si>
+  <si>
+    <t>NLI4VolVis: Natural Language Interaction for Volume Visualization  via LLM Multi-Agents and Editable 3D Gaussian Splatting (VIS'25)</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2402.09727</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2406.14550</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2310.11511</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://aclanthology.org/2024.emnlp-main.321.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://dl.acm.org/doi/pdf/10.14778/3749646.3749713</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.vldb.org/pvldb/vol18/p3695-chai.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2508.03404</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2504.10036</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://viterbi-web.usc.edu/~sabek/pdf/25_workshop_serag.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2506.07675</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2412.01661</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.vldb.org/cidrdb/papers/2024/p6-singh.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2312.01454</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2508.01136</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2412.19113</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://dl.acm.org/doi/pdf/10.1145/3674399.3674436</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
+        <sz val="9"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1110,1269 +2278,150 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2408.02213</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2503.07884</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://ieeexplore.ieee.org/document/11113071</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2509.06298</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://dl.acm.org/doi/abs/10.14778/3659437.3659461</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2402.13610</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://ieeexplore.ieee.org/abstract/document/10597732</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2502.15182</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://sarcouncil.com/download-article/SJECS-221-2025-769-775.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2502.20657</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2504.02059</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://aclanthology.org/2023.emnlp-main.574/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2412.10422</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2412.06724</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.vldb.org/2025/Workshops/VLDB-Workshops-2025/DATAI/DATAI25_8.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2503.06664</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.vldb.org/pvldb/vol18/p2371-tang.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2312.00326</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2501.11441</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2405.16884</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2502.14913</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2502.00675</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.databricks.com/blog/introducing-databricks-assistant-data-science-agent</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://github.com/jd-opensource/joyagent-jdgenie/tree/data_agent</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://cloud.google.com/blog/products/data-analytics/a-closer-look-at-bigquery-data-engineering-agent</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.volcengine.com/product/DataAgent</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://xata.io/blog/dba-to-db-agent</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://docs.snowflake.com/en/user-guide/snowflake-cortex/cortex-agents</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/abs/2510.16872v1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2508.05002</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>http://sites.computer.org/debull/A25mar/p57.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.vldb.org/cidrdb/papers/2025/p32-wang.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://arxiv.org/pdf/2402.18679</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://dl.acm.org/doi/10.14778/3750601.3750610</t>
-    </r>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Sub-domain</t>
-  </si>
-  <si>
-    <t>Data Agent</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>Venue</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Data Management</t>
-  </si>
-  <si>
-    <t>Configuration Tuning</t>
-  </si>
-  <si>
-    <t>LLMTune</t>
-  </si>
-  <si>
-    <t>LLMTune: Accelerate Database Knob Tuning with Large Language Models</t>
-  </si>
-  <si>
-    <t>arXiv</t>
-  </si>
-  <si>
-    <t>λ-Tune</t>
-  </si>
-  <si>
-    <t>λ-Tune: Harnessing Large Language Models for Automated Database System Tuning</t>
-  </si>
-  <si>
-    <t>SIGMOD</t>
-  </si>
-  <si>
-    <t>LATuner</t>
-  </si>
-  <si>
-    <t>LATuner: An LLM-Enhanced Database Tuning System Based on Adaptive Surrogate Model</t>
-  </si>
-  <si>
-    <t>ECML PKDD</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>GPTuner</t>
-  </si>
-  <si>
-    <t>GPTuner: A Manual-Reading Database Tuning System via GPT-Guided Bayesian Optimization</t>
-  </si>
-  <si>
-    <t>VLDB</t>
-  </si>
-  <si>
-    <t>E2ETune</t>
-  </si>
-  <si>
-    <t>E2ETune: End-to-End Knob Tuning via Fine-tuned Generative Language Model</t>
-  </si>
-  <si>
-    <t>Query Optimization</t>
-  </si>
-  <si>
-    <t>DB-GPT</t>
-  </si>
-  <si>
-    <t>DB-GPT: Large Language Model Meets Database</t>
-  </si>
-  <si>
-    <t>Data Science and Engineering</t>
-  </si>
-  <si>
-    <t>LLM-R2</t>
-  </si>
-  <si>
-    <t>LLM-R2: A Large Language Model Enhanced Rule-Based Rewrite System for Boosting Query Efficiency</t>
-  </si>
-  <si>
-    <t>GenRewriter</t>
-  </si>
-  <si>
-    <t>Query Rewriting via Large Language Models</t>
-  </si>
-  <si>
-    <t>LITHE</t>
-  </si>
-  <si>
-    <t>Query Rewriting via LLMs</t>
-  </si>
-  <si>
-    <t>LLM-QO</t>
-  </si>
-  <si>
-    <t>Can Large Language Models Be Query Optimizer for Relational Databases?</t>
-  </si>
-  <si>
-    <t>LLMOpt</t>
-  </si>
-  <si>
-    <t>A Query Optimization Method Utilizing Large Language Models</t>
-  </si>
-  <si>
-    <t>E3-Rewite</t>
-  </si>
-  <si>
-    <t>E3-Rewrite: Learning to Rewrite SQL for Executability, Equivalence, and Efficiency</t>
-  </si>
-  <si>
-    <t>System Diagnosis</t>
-  </si>
-  <si>
-    <t>DBG-PT</t>
-  </si>
-  <si>
-    <t>DBG-PT: A Large Language Model Assisted Query Performance Regression Debugger</t>
-  </si>
-  <si>
-    <t>Andromeda</t>
-  </si>
-  <si>
-    <t>Automatic Database Configuration Debugging using Retrieval-Augmented Language Models</t>
-  </si>
-  <si>
-    <t>Data Preparation</t>
-  </si>
-  <si>
-    <t>Data Cleaning</t>
-  </si>
-  <si>
-    <t>FM</t>
-  </si>
-  <si>
-    <t>Can Foundation Models Wrangle Your Data?</t>
-  </si>
-  <si>
-    <t>RetClean</t>
-  </si>
-  <si>
-    <t>RetClean: Retrieval-Based Data Cleaning Using LLMs and Data Lakes</t>
-  </si>
-  <si>
-    <t>VLDB demo</t>
-  </si>
-  <si>
-    <t>LakeFill</t>
-  </si>
-  <si>
-    <t>Data Imputation with Limited Data Redundancy Using Data Lakes</t>
-  </si>
-  <si>
-    <t>UniDM</t>
-  </si>
-  <si>
-    <t>MLSys</t>
-  </si>
-  <si>
-    <t>LLMClean</t>
-  </si>
-  <si>
-    <t>LLMClean: Context-Aware Tabular Data Cleaning via LLM-Generated OFDs</t>
-  </si>
-  <si>
-    <t>ADBIS</t>
-  </si>
-  <si>
-    <t>Data Integration</t>
-  </si>
-  <si>
-    <t>Table-GPT</t>
-  </si>
-  <si>
-    <t>Table-GPT: Table-tuned GPT for Diverse Table Tasks</t>
-  </si>
-  <si>
-    <t>BATCHER</t>
-  </si>
-  <si>
-    <t>Cost-Effective In-Context Learning for Entity Resolution: A Design Space Exploration</t>
-  </si>
-  <si>
-    <t>ICDE</t>
-  </si>
-  <si>
-    <t>Jellyfish</t>
-  </si>
-  <si>
-    <t>Jellyfish: Instruction-Tuning Local Large Language Models for Data Preprocessing</t>
-  </si>
-  <si>
-    <t>EMNLP</t>
-  </si>
-  <si>
-    <t>Data Discovery</t>
-  </si>
-  <si>
-    <t>ArcheType</t>
-  </si>
-  <si>
-    <t>ArcheType: A Novel Framework for Open-Source Column Type Annotation using Large Language Models</t>
-  </si>
-  <si>
-    <t>RACOON</t>
-  </si>
-  <si>
-    <t>RACOON: An LLM-based Framework for Retrieval-Augmented Column Type Annotation with a Knowledge Graph</t>
-  </si>
-  <si>
-    <t>Cocoon</t>
-  </si>
-  <si>
-    <t>Cocoon: Semantic table profiling using large language model</t>
-  </si>
-  <si>
-    <t>HILDA</t>
-  </si>
-  <si>
-    <t>AutoDDG</t>
-  </si>
-  <si>
-    <t>Autoddg: Automated dataset description generation using large language models</t>
-  </si>
-  <si>
-    <t>Pneuma</t>
-  </si>
-  <si>
-    <t>Pneuma: Leveraging llms for tabular data representation and retrieval in an end-to-end system</t>
-  </si>
-  <si>
-    <t>LLMCTA</t>
-  </si>
-  <si>
-    <t>Evaluating Knowledge Generation and Self-refinement Strategies for LLM-Based Column Type Annotation</t>
-  </si>
-  <si>
-    <t>Columbo</t>
-  </si>
-  <si>
-    <t>Columbo: Expanding Abbreviated Column Names for Tabular Data Using Large Language Models</t>
-  </si>
-  <si>
-    <t>Data Analysis</t>
-  </si>
-  <si>
-    <t>TableQA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dater </t>
-  </si>
-  <si>
-    <t>Large Language Models are Versatile Decomposers: Decomposing Evidence and Questions for Table-based Reasoning</t>
-  </si>
-  <si>
-    <t>SIGIR</t>
-  </si>
-  <si>
-    <t>BINDER</t>
-  </si>
-  <si>
-    <t>Binding Language Models in Symbolic Languages</t>
-  </si>
-  <si>
-    <t>ICLR</t>
-  </si>
-  <si>
-    <t>Self-augmented Prompting</t>
-  </si>
-  <si>
-    <t>Table Meets LLM: Can Large Language Models Understand Structured Table Data? A Benchmark and Empirical Study</t>
-  </si>
-  <si>
-    <t>WSDM</t>
-  </si>
-  <si>
-    <t>TableLlama</t>
-  </si>
-  <si>
-    <t>TableLlama: Towards Open Large Generalist Models for Tables</t>
-  </si>
-  <si>
-    <t>NAACL</t>
-  </si>
-  <si>
-    <t>NL2SQL</t>
-  </si>
-  <si>
-    <t>DIN-SQL</t>
-  </si>
-  <si>
-    <t>DIN-SQL: Decomposed In-Context Learning of Text-to-SQL with Self-Correction.</t>
-  </si>
-  <si>
-    <t>NeurIPS</t>
-  </si>
-  <si>
-    <t>DAIL-SQL</t>
-  </si>
-  <si>
-    <t>Text-to-SQL Empowered by Large Language Models: A Benchmark Evaluation</t>
-  </si>
-  <si>
-    <t>ACT-SQL</t>
-  </si>
-  <si>
-    <t>ACT-SQL: In-Context Learning for Text-to-SQL with Automatically-Generated Chain-of-Thought</t>
-  </si>
-  <si>
-    <t>SuperSQL</t>
-  </si>
-  <si>
-    <t>The Dawn of Natural Language to SQL: Are We Fully Ready?</t>
-  </si>
-  <si>
-    <t>NL2VIS</t>
-  </si>
-  <si>
-    <t>Chat2VIS</t>
-  </si>
-  <si>
-    <t>Chat2VIS: Generating Data Visualizations via Natural Language Using ChatGPT, Codex and GPT-3 Large Language Models</t>
-  </si>
-  <si>
-    <t>IEEE Access</t>
-  </si>
-  <si>
-    <t>NL4DV-LLM</t>
-  </si>
-  <si>
-    <t>Generating Analytic Specifications for Data Visualization from Natural Language Queries using Large Language Models</t>
-  </si>
-  <si>
-    <t>VIS</t>
-  </si>
-  <si>
-    <t>Prompt4Vis</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Step-Text2Vis</t>
-  </si>
-  <si>
-    <t>nvBench 2.0: Resolving Ambiguity in Text-to-Visualization through Stepwise Reasoning</t>
-  </si>
-  <si>
-    <t>NeuRIPS</t>
-  </si>
-  <si>
-    <t>Unstructured Data Analysis</t>
-  </si>
-  <si>
-    <t>LongRAG</t>
-  </si>
-  <si>
-    <t>LongRAG: A Dual-Perspective Retrieval-Augmented Generation Paradigm for Long-Context Question Answering</t>
-  </si>
-  <si>
-    <t>RAPTOR</t>
-  </si>
-  <si>
-    <t>RAPTOR: Recursive Abstractive Processing for Tree-Organized Retrieval</t>
-  </si>
-  <si>
-    <t>PDFTriage</t>
-  </si>
-  <si>
-    <t>PDFTriage: Question Answering over Long, Structured Documents</t>
-  </si>
-  <si>
-    <t>DSE</t>
-  </si>
-  <si>
-    <t>Unifying Multimodal Retrieval via Document Screenshot Embedding</t>
-  </si>
-  <si>
-    <t>VisDoM</t>
-  </si>
-  <si>
-    <t>VisDoM: Multi-Document QA with Visually Rich Elements Using Multimodal Retrieval-Augmented Generation</t>
-  </si>
-  <si>
-    <t>Docopilot</t>
-  </si>
-  <si>
-    <t>Docopilot: Improving Multimodal Models for Document-Level Understanding</t>
-  </si>
-  <si>
-    <t>CVPR</t>
-  </si>
-  <si>
-    <t>Report Generation</t>
-  </si>
-  <si>
-    <t>Datatales</t>
-  </si>
-  <si>
-    <t>DataTales: Investigating the use of Large Language Models for Authoring Data-Driven Articles</t>
-  </si>
-  <si>
-    <t>Choe et al.</t>
-  </si>
-  <si>
-    <t>Enhancing Data Literacy On-demand: LLMs as Guides for Novices in Chart Interpretation</t>
-  </si>
-  <si>
-    <t>TVCG</t>
-  </si>
-  <si>
-    <t>ReportGPT</t>
-  </si>
-  <si>
-    <t>ReportGPT: Human‑in‑the‑Loop Verifiable Table‑to‑Text Generation</t>
-  </si>
-  <si>
-    <t>EMNLP Industry</t>
-  </si>
-  <si>
-    <t>InterChat</t>
-  </si>
-  <si>
-    <t>InterChat: Enhancing Generative Visual Analytics using Multimodal Interactions</t>
-  </si>
-  <si>
-    <t>EuroVis</t>
-  </si>
-  <si>
-    <t>VizTA</t>
-  </si>
-  <si>
-    <t>VizTA: Enhancing Comprehension of Distributional Visualization with Visual-Lexical Fused Conversational Interface</t>
-  </si>
-  <si>
-    <t>ChartLens</t>
-  </si>
-  <si>
-    <t>ChartLens: Fine-grained Visual Attribution in Charts</t>
-  </si>
-  <si>
-    <t>ACL</t>
-  </si>
-  <si>
-    <t>Li et al.</t>
-  </si>
-  <si>
-    <t>Is Large Language Model Good at Database Knob Tuning? A Comprehensive Experimental Evaluation</t>
-  </si>
-  <si>
-    <t>LLMIdxAdvis</t>
-  </si>
-  <si>
-    <t>LLMIdxAdvis: Resource-Efficient Index Advisor Utilizing Large Language Model</t>
-  </si>
-  <si>
-    <t>RABBIT</t>
-  </si>
-  <si>
-    <t>Rabbit: Retrieval-Augmented Generation Enables Better Automatic Database Knob Tuning</t>
-  </si>
-  <si>
-    <t>MCTuner</t>
-  </si>
-  <si>
-    <t>MCTuner: Spatial Decomposition-Enhanced Database Tuning via LLM-Guided Exploration</t>
-  </si>
-  <si>
-    <t>SERAG</t>
-  </si>
-  <si>
-    <t>SERAG: Self-Evolving RAG System for Query Optimization</t>
-  </si>
-  <si>
-    <t>SIGMOD Workshop</t>
-  </si>
-  <si>
-    <t>QUITE</t>
-  </si>
-  <si>
-    <t>QUITE: A Query Rewrite System Beyond Rules with LLM Agents</t>
-  </si>
-  <si>
-    <t>R-Bot</t>
-  </si>
-  <si>
-    <t>R-Bot: An LLM-Based Query Rewrite System</t>
-  </si>
-  <si>
-    <t>Panda</t>
-  </si>
-  <si>
-    <t>Panda: Performance Debugging for Databases using LLM Agents</t>
-  </si>
-  <si>
-    <t>CIDR</t>
-  </si>
-  <si>
-    <t>D-Bot</t>
-  </si>
-  <si>
-    <t>D-Bot: Database Diagnosis System using Large Language Models</t>
-  </si>
-  <si>
-    <t>DBAIOps</t>
-  </si>
-  <si>
-    <t>DBAIOps: A Reasoning LLM-Enhanced Database Operation and Maintenance System using Knowledge Graphs</t>
-  </si>
-  <si>
-    <t>SketchFill</t>
-  </si>
-  <si>
-    <t>SketchFill: Sketch-Guided Code Generation for Imputing Derived Missing Values</t>
-  </si>
-  <si>
-    <t>IterClean</t>
-  </si>
-  <si>
-    <t>IterClean: An Iterative Data Cleaning Framework with Large Language Models</t>
-  </si>
-  <si>
-    <t>ACM-TURC</t>
-  </si>
-  <si>
-    <t>AutoPrep</t>
-  </si>
-  <si>
-    <t>AutoPrep: Natural Language Question-Aware Data Preparation with a Multi-Agent Framework</t>
-  </si>
-  <si>
-    <t>AutoDCWorkflow</t>
-  </si>
-  <si>
-    <t>AutoDCWorkflow: LLM-based Data Cleaning Workflow Auto-Generation and Benchmark</t>
-  </si>
-  <si>
-    <t>EMNLP Findings</t>
-  </si>
-  <si>
-    <t>CleanAgent</t>
-  </si>
-  <si>
-    <t>CleanAgent: Automating Data Standardization with LLM-based Agents</t>
-  </si>
-  <si>
-    <t>VLDB Workshop</t>
-  </si>
-  <si>
-    <t>Bendinelli et al.</t>
-  </si>
-  <si>
-    <t>Exploring LLM Agents for Cleaning Tabular Machine Learning Datasets</t>
-  </si>
-  <si>
-    <t>ICLR Workshop</t>
-  </si>
-  <si>
-    <t>MegaTran</t>
-  </si>
-  <si>
-    <t>Weak-to-Strong Prompts with Lightweight-to-Powerful LLMs for High-Accuracy, Low-Cost, and Explainable Data Transformation</t>
-  </si>
-  <si>
-    <t>Agent-OM</t>
-  </si>
-  <si>
-    <t>Agent-OM: Leveraging LLM Agents for Ontology Matching</t>
-  </si>
-  <si>
-    <t>MILA</t>
-  </si>
-  <si>
-    <t>Ontology Matching with Large Language Models and Prioritized Depth-First Search</t>
-  </si>
-  <si>
-    <t>Information Fusion</t>
-  </si>
-  <si>
-    <t>COMEM</t>
-  </si>
-  <si>
-    <t>Match, Compare, or Select? An Investigation of Large Language Models for Entity Matching</t>
-  </si>
-  <si>
-    <t>COLING</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Chorus</t>
-  </si>
-  <si>
-    <t>Chorus: Foundation Models for Unified Data Discovery and Exploration</t>
-  </si>
-  <si>
-    <t>DataVoyager</t>
-  </si>
-  <si>
-    <t>Data-driven Discovery with Large Generative Models</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DATALORE </t>
-  </si>
-  <si>
-    <t>DATALORE: Can a Large Language Model Find All Lost Scrolls in a Data Repository?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LEDD</t>
-  </si>
-  <si>
-    <t>LEDD: Large Language Model-Empowered Data Discovery in Data Lakes</t>
-  </si>
-  <si>
-    <t>MetaGen</t>
-  </si>
-  <si>
-    <t>Automated Metadata Generation Using Large Language Models: A GPT-4 Case Study for Enterprise Data Profiling</t>
-  </si>
-  <si>
-    <t>Journal for Engineering and Computer Science</t>
-  </si>
-  <si>
-    <t>DBDescGen</t>
-  </si>
-  <si>
-    <t>Automatic database description generation for Text-to-SQL</t>
-  </si>
-  <si>
-    <t>Wang et al.</t>
-  </si>
-  <si>
-    <t>Towards Operationalizing Heterogeneous Data Discovery</t>
-  </si>
-  <si>
-    <t>StructGPT</t>
-  </si>
-  <si>
-    <t>StructGPT: A General Framework for Large Language Model to Reason over Structured Data</t>
-  </si>
-  <si>
-    <t>ReAcTable</t>
-  </si>
-  <si>
-    <t>ReAcTable: Enhancing ReAct for Table Question Answering</t>
-  </si>
-  <si>
-    <t>CHAIN-OF-TABLE</t>
-  </si>
-  <si>
-    <t>Chain-of-Table: Evolving Tables in the Reasoning Chain for Table Understanding</t>
-  </si>
-  <si>
-    <t>AutoTQA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AutoTQA: Towards Autonomous Tabular Question Answering through Multi-Agent Large Language Models</t>
-  </si>
-  <si>
-    <t>Table-Critic</t>
-  </si>
-  <si>
-    <t>Table-Critic: A Multi-Agent Framework for Collaborative Criticism and Refinement in Table Reasoning</t>
-  </si>
-  <si>
-    <t>MAC-SQL</t>
-  </si>
-  <si>
-    <t>MAC-SQL: A Multi-Agent Collaborative Framework for Text-to-SQL</t>
-  </si>
-  <si>
-    <t>ChatBI</t>
-  </si>
-  <si>
-    <t>Chatbi: Towards natural language to complex business</t>
-  </si>
-  <si>
-    <t>Chase-SQL</t>
-  </si>
-  <si>
-    <t>CHASE-SQL: Multi-Path Reasoning and Preference Optimized Candidate Selection in Text-to-SQL</t>
-  </si>
-  <si>
-    <t>Alpha-SQL</t>
-  </si>
-  <si>
-    <t>Alpha-SQL: Zero-Shot Text-to-SQL using Monte Carlo Tree Search</t>
-  </si>
-  <si>
-    <t>ICML</t>
-  </si>
-  <si>
-    <t>OpenSearch-SQL</t>
-  </si>
-  <si>
-    <t>OpenSearch-SQL: Enhancing Text-to-SQL with Dynamic Few-shot and Consistency Alignment.</t>
-  </si>
-  <si>
-    <t>ReFoRCE</t>
-  </si>
-  <si>
-    <t>DeepEye-SQL</t>
-  </si>
-  <si>
-    <t>DeepEye-SQL: A Software-Engineering-Inspired Text-to-SQL Framework</t>
-  </si>
-  <si>
-    <t>MatPlotAgent</t>
-  </si>
-  <si>
-    <t>MatPlotAgent: Method and Evaluation for LLM-Based Agentic Scientific Data Visualization</t>
-  </si>
-  <si>
-    <t>Text2Chart31</t>
-  </si>
-  <si>
-    <t>Text2Chart31: Instruction Tuning for Chart Generation with Automatic Feedback</t>
-  </si>
-  <si>
-    <t>nvAgent</t>
-  </si>
-  <si>
-    <t>NVAGENT: Automated Data Visualization from Natural Language via Collaborative Agent Workflow</t>
-  </si>
-  <si>
-    <t>DeepVIS</t>
-  </si>
-  <si>
-    <t>DeepVIS: Bridging Natural Language and Data Visualization Through Step-wise Reasoning</t>
-  </si>
-  <si>
-    <t>FLARE</t>
-  </si>
-  <si>
-    <t>Active Retrieval Augmented Generation</t>
-  </si>
-  <si>
-    <t>ReadAgent</t>
-  </si>
-  <si>
-    <t>A Human-Inspired Reading Agent with Gist Memory of Very Long Contexts</t>
-  </si>
-  <si>
-    <t>GraphReader</t>
-  </si>
-  <si>
-    <t>GraphReader: Building Graph-based Agent to Enhance Long-Context Abilities of Large Language Models</t>
-  </si>
-  <si>
-    <t>Self-RAG</t>
-  </si>
-  <si>
-    <t>Self-RAG: Learning to Retrieve, Generate, and Critique through Self-Reflection</t>
-  </si>
-  <si>
-    <t>REAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REAR: A Relevance-Aware Retrieval-Augmented Framework for Open-Domain Question Answering </t>
-  </si>
-  <si>
-    <t>QUEST</t>
-  </si>
-  <si>
-    <t>QUEST: Query Optimization in Unstructured Document Analysis</t>
-  </si>
-  <si>
-    <t>Doctopus</t>
-  </si>
-  <si>
-    <t>Doctopus: Budget-aware Structural Table Extraction from Unstructured Documents</t>
-  </si>
-  <si>
-    <t>MACT</t>
-  </si>
-  <si>
-    <t>Visual Document Understanding and Question Answering: A Multi-Agent Collaboration Framework with Test-Time Scaling</t>
-  </si>
-  <si>
-    <t>DataPuzzle</t>
-  </si>
-  <si>
-    <t>DataPuzzle: Breaking Free from the Hallucinated Promise of LLMs in Data Analysis</t>
-  </si>
-  <si>
-    <t>DataNarrative</t>
-  </si>
-  <si>
-    <t>DataNarrative: Automated Data-Driven Storytelling with Visualizations and Texts</t>
-  </si>
-  <si>
-    <t>Data Director</t>
-  </si>
-  <si>
-    <t>From Data to Story: Towards Automatic Animated Data Video Creation with LLM-based Multi-Agent Systems</t>
-  </si>
-  <si>
-    <t>VIS  workshop</t>
-  </si>
-  <si>
-    <t>LightVA</t>
-  </si>
-  <si>
-    <t>LightVA: Lightweight Visual Analytics with LLM Agent-Based Task Planning and Execution</t>
-  </si>
-  <si>
-    <t>Multimodal DeepResearcher</t>
-  </si>
-  <si>
-    <t>Multimodal DeepResearcher: Generating Text–Chart Interleaved Reports with an Agentic Framework</t>
-  </si>
-  <si>
-    <t>DAgent</t>
-  </si>
-  <si>
-    <t>DAgent: A Relational Database-Driven Data Analysis Report Generation Agent</t>
-  </si>
-  <si>
-    <t>Chart Insighter</t>
-  </si>
-  <si>
-    <t>ChartInsighter: An Approach for Mitigating Hallucination in Time-Series Chart Summary Generation With a Benchmark Dataset</t>
-  </si>
-  <si>
-    <t>ProactiveVA</t>
-  </si>
-  <si>
-    <t>ProactiveVA: Proactive Visual Analytics with LLM-Based UI Agent</t>
-  </si>
-  <si>
-    <t>VOICE</t>
-  </si>
-  <si>
-    <t>VOICE: Visual Oracle for Interaction, Conversation, and Explanation</t>
-  </si>
-  <si>
-    <t>NLI4VolVis</t>
-  </si>
-  <si>
-    <t>NLI4VolVis: Natural Language Interaction for Volume Visualization  via LLM Multi-Agents and Editable 3D Gaussian Splatting (VIS'25)</t>
-  </si>
-  <si>
     <t>Affiliation</t>
   </si>
   <si>
+    <t>A Survey of Text-to-SQL in the Era of LLMs: Where are we, and where are we going?</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/11095853</t>
+  </si>
+  <si>
+    <t>TKDE</t>
+  </si>
+  <si>
+    <t>Natural Language to SQL: State of the Art and Open Problems</t>
+  </si>
+  <si>
+    <t>https://www.vldb.org/pvldb/vol18/p5466-luo.pdf</t>
+  </si>
+  <si>
+    <t>VLDB Tutorial</t>
+  </si>
+  <si>
+    <t>A Survey of LLM × DATA</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2505.18458</t>
+  </si>
+  <si>
+    <t>LLM/Agent-as-Data-Analyst: A Survey</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2509.23988</t>
+  </si>
+  <si>
+    <t>Large Language Model-based Data Science Agent: A Survey</t>
+  </si>
+  <si>
+    <t>https://www.arxiv.org/abs/2508.02744</t>
+  </si>
+  <si>
+    <t>LLM-Based Data Science Agents: A Survey of Capabilities, Challenges, and Future Directions</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2510.04023</t>
+  </si>
+  <si>
+    <t>Large Language Models for Data Science: A Survey</t>
+  </si>
+  <si>
+    <t>https://rgdoi.net/10.13140/RG.2.2.14003.75042</t>
+  </si>
+  <si>
+    <t>A Survey on Large Language Model-based Agents for Statistics and Data Science</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2412.14222</t>
+  </si>
+  <si>
+    <t>The American Statistician</t>
+  </si>
+  <si>
+    <t>Large Language Models for Data Discovery and Integration: Challenges and Opportunities</t>
+  </si>
+  <si>
+    <t>http://sites.computer.org/debull/A25mar/p3.pdf</t>
+  </si>
+  <si>
+    <t>IEEE Data Eng. Bull.</t>
+  </si>
+  <si>
+    <t>Data+AI: LLM4Data and Data4LLM</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/pdf/10.1145/3722212.3725641</t>
+  </si>
+  <si>
+    <t>SIGMOD Tutorial</t>
+  </si>
+  <si>
+    <t>LLM for Data Management</t>
+  </si>
+  <si>
+    <t>https://www.vldb.org/pvldb/vol17/p4213-li.pdf</t>
+  </si>
+  <si>
+    <t>Large Language Models for Data Annotation and Synthesis: A Survey</t>
+  </si>
+  <si>
+    <t>https://aclanthology.org/2024.emnlp-main.54.pdf</t>
+  </si>
+  <si>
+    <t>Data Management for Machine Learning: A Survey</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/9705125</t>
+  </si>
+  <si>
+    <t>LLM As DBA</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2308.05481</t>
+  </si>
+  <si>
+    <t>Demystifying Artificial Intelligence for Data Preparation</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/pdf/10.1145/3555041.3589406</t>
+  </si>
+  <si>
+    <t>DeepEye</t>
+  </si>
+  <si>
+    <t>DeepEye: A Steerable Self-driving Data Agent System</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2603.28889</t>
+  </si>
+  <si>
+    <t>SIGMOD Demo</t>
+  </si>
+  <si>
+    <t>HKUST(GZ)</t>
+  </si>
+  <si>
+    <t>DataEvolver</t>
+  </si>
+  <si>
+    <t>DataEvolver: Automatic Data Preparation for Large Language Models through Multi-Level Self-Evolving</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2606.07001</t>
+  </si>
+  <si>
+    <t>RUC</t>
+  </si>
+  <si>
     <t>AgenticData</t>
   </si>
   <si>
     <t>AgenticData: An Agentic Data Analytics System for Heterogeneous Data</t>
   </si>
   <si>
+    <t>https://arxiv.org/pdf/2508.05002</t>
+  </si>
+  <si>
     <t>Tsinghua University</t>
   </si>
   <si>
@@ -2382,13 +2431,28 @@
     <t>DeepAnalyze: Agentic Large Language Models for Autonomous Data Science</t>
   </si>
   <si>
-    <t>RUC</t>
+    <t>https://arxiv.org/abs/2510.16872v1</t>
+  </si>
+  <si>
+    <t>DataMind</t>
+  </si>
+  <si>
+    <t>Scaling Generalist Data-Analytic Agents</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2509.25084</t>
+  </si>
+  <si>
+    <t>ZJU</t>
   </si>
   <si>
     <t>AOP</t>
   </si>
   <si>
-    <t xml:space="preserve">AOP: Automated and Interactive LLM Pipeline Orchestration for Answering Complex Queries </t>
+    <t>AOP: Automated and Interactive LLM Pipeline Orchestration for Answering Complex Queries</t>
+  </si>
+  <si>
+    <t>https://www.vldb.org/cidrdb/papers/2025/p32-wang.pdf</t>
   </si>
   <si>
     <t>iDataLake</t>
@@ -2397,6 +2461,9 @@
     <t>iDataLake: An LLM-Powered Analytics System on Data Lakes</t>
   </si>
   <si>
+    <t>http://sites.computer.org/debull/A25mar/p57.pdf</t>
+  </si>
+  <si>
     <t>IEEE Data Engineering Bulletin</t>
   </si>
   <si>
@@ -2406,323 +2473,97 @@
     <t>SiriusBI: A Comprehensive LLM-Powered Solution for Data Analytics in Business Intelligence</t>
   </si>
   <si>
+    <t>https://dl.acm.org/doi/10.14778/3750601.3750610</t>
+  </si>
+  <si>
+    <t>Tencent</t>
+  </si>
+  <si>
     <t>Data Interpreter</t>
   </si>
   <si>
     <t>Data Interpreter: An LLM Agent For Data Science</t>
   </si>
   <si>
+    <t>https://arxiv.org/pdf/2402.18679</t>
+  </si>
+  <si>
+    <t>ACL Findings</t>
+  </si>
+  <si>
     <t>DeepWisdom</t>
   </si>
   <si>
     <t>JoyAgent</t>
   </si>
   <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>https://github.com/jd-opensource/joyagent-jdgenie/tree/data_agent</t>
+  </si>
+  <si>
+    <t>JDCHO</t>
+  </si>
+  <si>
     <t>Assist. DS Agent</t>
   </si>
   <si>
+    <t>https://www.databricks.com/blog/introducing-databricks-assistant-data-science-agent</t>
+  </si>
+  <si>
     <t>Databricks</t>
   </si>
   <si>
+    <t>https://www.volcengine.com/product/DataAgent</t>
+  </si>
+  <si>
     <t>Bytedance</t>
   </si>
   <si>
     <t>BigQuery</t>
   </si>
   <si>
+    <t>https://cloud.google.com/blog/products/data-analytics/a-closer-look-at-bigquery-data-engineering-agent</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
     <t>Cortex</t>
   </si>
   <si>
+    <t>https://docs.snowflake.com/en/user-guide/snowflake-cortex/cortex-agents</t>
+  </si>
+  <si>
     <t>Snowflake</t>
   </si>
   <si>
     <t>Xata Agent (Just DBA)</t>
   </si>
   <si>
+    <t>https://xata.io/blog/dba-to-db-agent</t>
+  </si>
+  <si>
     <t>Xata</t>
   </si>
   <si>
-    <t>/</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>arXiv</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>VLDB</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACL Findings</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>JDCHO</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tencent</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>A Survey of Text-to-SQL in the Era of LLMs: Where are we, and where are we going?</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/document/11095853</t>
-  </si>
-  <si>
-    <t>TKDE</t>
-  </si>
-  <si>
-    <t>Natural Language to SQL: State of the Art and Open Problems</t>
-  </si>
-  <si>
-    <t>https://www.vldb.org/pvldb/vol18/p5466-luo.pdf</t>
-  </si>
-  <si>
-    <t>VLDB Tutorial</t>
-  </si>
-  <si>
-    <t>A Survey of LLM × DATA</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2505.18458</t>
-  </si>
-  <si>
-    <t>LLM/Agent-as-Data-Analyst: A Survey</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2509.23988</t>
-  </si>
-  <si>
-    <t>https://www.arxiv.org/abs/2508.02744</t>
-  </si>
-  <si>
-    <t>LLM-Based Data Science Agents: A Survey of Capabilities, Challenges, and Future Directions</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2510.04023</t>
-  </si>
-  <si>
-    <t>Large Language Models for Data Science: A Survey</t>
-  </si>
-  <si>
-    <t>https://rgdoi.net/10.13140/RG.2.2.14003.75042</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2412.14222</t>
-  </si>
-  <si>
-    <t>The American Statistician</t>
-  </si>
-  <si>
-    <t>Large Language Models for Data Discovery and Integration: Challenges and Opportunities</t>
-  </si>
-  <si>
-    <t>http://sites.computer.org/debull/A25mar/p3.pdf</t>
-  </si>
-  <si>
-    <t>IEEE Data Eng. Bull.</t>
-  </si>
-  <si>
-    <t>Data+AI: LLM4Data and Data4LLM</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/pdf/10.1145/3722212.3725641</t>
-  </si>
-  <si>
-    <t>SIGMOD Tutorial</t>
-  </si>
-  <si>
-    <t>LLM for Data Management</t>
-  </si>
-  <si>
-    <t>https://www.vldb.org/pvldb/vol17/p4213-li.pdf</t>
-  </si>
-  <si>
-    <t>Large Language Models for Data Annotation and Synthesis: A Survey</t>
-  </si>
-  <si>
-    <t>https://aclanthology.org/2024.emnlp-main.54.pdf</t>
-  </si>
-  <si>
-    <t>Data Management for Machine Learning: A Survey</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/document/9705125</t>
-  </si>
-  <si>
-    <t>LLM As DBA</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/pdf/2308.05481</t>
-  </si>
-  <si>
-    <t>Demystifying Artificial Intelligence for Data Preparation</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/pdf/10.1145/3555041.3589406</t>
-  </si>
-  <si>
-    <t>CIDR</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Large Language Model-based Data Science Agent: A Survey</t>
-  </si>
-  <si>
-    <t>A Survey on Large Language Model-based Agents for Statistics and Data Science</t>
-  </si>
-  <si>
-    <t>NeurIPS</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ST-Raptor</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ST-Raptor: LLM-Powered Semi-Structured Table Question Answering</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2508.18190</t>
-  </si>
-  <si>
-    <t>SIGMOD</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cracking SQL Barriers: An LLM-based Dialect Translation System</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/10.1145/3725278</t>
-  </si>
-  <si>
-    <t>CrackSQL</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReFoRCE: A Text-to-SQL Agent with Self-Refinement, Consensus Enforcement, and Column Exploration</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AgentTune: An Agent-Based Large Language Model Framework for Database Knob Tuning</t>
-  </si>
-  <si>
-    <t>AgentTune</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/10.1145/3769758</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prompt4Vis: Prompting Large Language Models with Example Mining for Tabular Data Visualization</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>VLDBJ</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unidm: A unified framework for data manipulation with large language models</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s00778-025-00912-0</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>New</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MultiVis-Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Multi-Agent Framework with Logic Rules for Reliable and Comprehensive Cross-Modal Data Visualization</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2601.18320</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/epdf/10.1145/3769771</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DeepPrep</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DeepPrep: An LLM-Powered Agentic System for Autonomous Data Preparation</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://arxiv.org/pdf/2602.07371</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ICLR</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZJU</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://arxiv.org/pdf/2509.25084</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scaling Generalist Data-Analytic Agents</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DataMind</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DeepEye</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HKUST(GZ)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DeepEye: A Steerable Self-driving Data Agent System</t>
+    <t>Julius.ai</t>
+  </si>
+  <si>
+    <t>https://julius.ai/</t>
   </si>
   <si>
     <t>Julis</t>
   </si>
   <si>
-    <t>Julius.ai</t>
-  </si>
-  <si>
     <t>Bayeslab.ai</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bayeslab.ai/</t>
   </si>
   <si>
     <t>Bayeslab</t>
-  </si>
-  <si>
-    <t>https://julius.ai/</t>
-  </si>
-  <si>
-    <t>https://bayeslab.ai/</t>
-  </si>
-  <si>
-    <t>SIGMOD Demo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://arxiv.org/pdf/2603.28889</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2734,82 +2575,65 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.75"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9.75"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9.75"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9.75"/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="12.75"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="9.75"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2817,23 +2641,21 @@
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9.75"/>
+      <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="10"/>
       <color theme="10"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -2842,7 +2664,6 @@
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2850,7 +2671,19 @@
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="FangSong"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="59">
@@ -3138,13 +2971,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6425D0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE1EAFF"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3629,7 +3460,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3794,94 +3625,94 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="40" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="40" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="50" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="50" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="48" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="48" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="52" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="52" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="36" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="36" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="57" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="57" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="66" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="66" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3893,16 +3724,16 @@
     <xf numFmtId="0" fontId="1" fillId="33" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="58" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="58" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="58" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="58" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="58" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="58" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="34" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3911,25 +3742,25 @@
     <xf numFmtId="0" fontId="1" fillId="39" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="65" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="65" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="46" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="46" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3938,16 +3769,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="56" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3956,7 +3787,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="超链接" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3972,7 +3803,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -4012,110 +3843,16 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office 2013 - 2022">
@@ -4123,80 +3860,31 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -4226,22 +3914,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -4258,19 +3946,11 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846891F3-6241-104A-907C-8714B014AF18}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H237"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
@@ -4282,1066 +3962,1062 @@
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14">
+    <row r="1" spans="1:8">
       <c r="A1" s="29" t="s">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="C1" s="80" t="s">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="F1" s="29" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="G1" s="29" t="s">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="H1" s="29" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="8" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G2" s="27">
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="19" customHeight="1">
+    <row r="3" spans="1:8" ht="25.25" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="27"/>
       <c r="C3" s="54" t="s">
-        <v>136</v>
+        <v>14</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="G3" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="19" customHeight="1">
+    <row r="4" spans="1:8" ht="25.25" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="27"/>
       <c r="C4" s="55" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="G4" s="27">
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="14">
-      <c r="A5" s="3" t="s">
-        <v>142</v>
-      </c>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3"/>
       <c r="B5" s="27"/>
       <c r="C5" s="54" t="s">
-        <v>143</v>
+        <v>22</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G5" s="27">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19" customHeight="1">
+    <row r="6" spans="1:8" ht="25.25" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="27"/>
       <c r="C6" s="54" t="s">
-        <v>146</v>
+        <v>26</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G6" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="19" customHeight="1">
+    <row r="7" spans="1:8" ht="25.25" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="27" t="s">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="G7" s="27">
         <v>2024</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="19" customHeight="1">
+    <row r="8" spans="1:8" ht="25.25" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="27"/>
       <c r="C8" s="54" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>153</v>
+        <v>35</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G8" s="27">
         <v>2024</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="19" customHeight="1">
+    <row r="9" spans="1:8" ht="25.25" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="27"/>
       <c r="C9" s="55" t="s">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G9" s="27">
         <v>2024</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="19" customHeight="1">
+    <row r="10" spans="1:8" ht="25.25" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="27"/>
       <c r="C10" s="55" t="s">
-        <v>156</v>
+        <v>40</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G10" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="19" customHeight="1">
+    <row r="11" spans="1:8" ht="25.25" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="27"/>
       <c r="C11" s="54" t="s">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
       <c r="E11" s="97" t="s">
-        <v>495</v>
+        <v>45</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>479</v>
+        <v>17</v>
       </c>
       <c r="G11" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19" customHeight="1">
+    <row r="12" spans="1:8" ht="25.25" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="27"/>
       <c r="C12" s="56" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G12" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="19" customHeight="1">
+    <row r="13" spans="1:8" ht="25.25" customHeight="1">
       <c r="A13" s="84"/>
       <c r="B13" s="86"/>
       <c r="C13" s="54" t="s">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>163</v>
+        <v>50</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G13" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="19" customHeight="1">
+    <row r="14" spans="1:8" ht="25.25" customHeight="1">
       <c r="A14" s="3"/>
       <c r="B14" s="27" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>165</v>
+        <v>53</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G14" s="27">
         <v>2024</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="19" customHeight="1">
+    <row r="15" spans="1:8" ht="25.25" customHeight="1">
       <c r="A15" s="3"/>
       <c r="B15" s="27"/>
       <c r="C15" s="54" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="G15" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="14">
+    <row r="16" spans="1:8">
       <c r="A16" s="8" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>172</v>
+        <v>62</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G16" s="16">
         <v>2022</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14">
-      <c r="A17" s="3" t="s">
-        <v>142</v>
-      </c>
+    <row r="17" spans="1:7">
+      <c r="A17" s="3"/>
       <c r="B17" s="16"/>
       <c r="C17" s="57" t="s">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>175</v>
+        <v>67</v>
       </c>
       <c r="G17" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="19" customHeight="1">
+    <row r="18" spans="1:7" ht="25.25" customHeight="1">
       <c r="A18" s="3"/>
       <c r="B18" s="16"/>
       <c r="C18" s="57" t="s">
-        <v>176</v>
+        <v>68</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>177</v>
+        <v>69</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G18" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="19" customHeight="1">
+    <row r="19" spans="1:7" ht="25.25" customHeight="1">
       <c r="A19" s="3"/>
       <c r="B19" s="16"/>
       <c r="C19" s="58" t="s">
-        <v>178</v>
+        <v>71</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>489</v>
+        <v>72</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="G19" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="19" customHeight="1">
+    <row r="20" spans="1:7" ht="25.25" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="16"/>
       <c r="C20" s="57" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="G20" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="19" customHeight="1">
+    <row r="21" spans="1:7" ht="25.25" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="35" t="s">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="C21" s="59" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="F21" s="35" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="G21" s="35">
         <v>2024</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="19" customHeight="1">
+    <row r="22" spans="1:7" ht="25.25" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="35"/>
       <c r="C22" s="59" t="s">
-        <v>186</v>
+        <v>83</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>188</v>
+        <v>86</v>
       </c>
       <c r="G22" s="35">
         <v>2024</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="19" customHeight="1">
+    <row r="23" spans="1:7" ht="25.25" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="35"/>
       <c r="C23" s="59" t="s">
-        <v>189</v>
+        <v>87</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G23" s="35">
         <v>2024</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="25" customHeight="1">
+    <row r="24" spans="1:7" ht="33.25" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="1" t="s">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>193</v>
+        <v>92</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>194</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G24" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="25" customHeight="1">
+    <row r="25" spans="1:7" ht="33.25" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="1"/>
       <c r="C25" s="61" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G25" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="19" customHeight="1">
+    <row r="26" spans="1:7" ht="25.25" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="1"/>
       <c r="C26" s="61" t="s">
-        <v>197</v>
+        <v>98</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>199</v>
+        <v>101</v>
       </c>
       <c r="G26" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="19" customHeight="1">
+    <row r="27" spans="1:7" ht="25.25" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="1"/>
       <c r="C27" s="60" t="s">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G27" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="19" customHeight="1">
+    <row r="28" spans="1:7" ht="25.25" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="60" t="s">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="G28" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="19" customHeight="1">
+    <row r="29" spans="1:7" ht="25.25" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="60" t="s">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>205</v>
+        <v>109</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="G29" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="25" customHeight="1">
+    <row r="30" spans="1:7" ht="33.25" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="61" t="s">
-        <v>206</v>
+        <v>111</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>207</v>
+        <v>112</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G30" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="19" customHeight="1">
+    <row r="31" spans="1:7" ht="25.25" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>208</v>
+        <v>114</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>209</v>
+        <v>115</v>
       </c>
       <c r="C31" s="62" t="s">
-        <v>210</v>
+        <v>116</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>211</v>
+        <v>117</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>212</v>
+        <v>119</v>
       </c>
       <c r="G31" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="19" customHeight="1">
+    <row r="32" spans="1:7" ht="25.25" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="7"/>
       <c r="C32" s="63" t="s">
-        <v>213</v>
+        <v>120</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>214</v>
+        <v>121</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>215</v>
+        <v>123</v>
       </c>
       <c r="G32" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="19" customHeight="1">
+    <row r="33" spans="1:7" ht="25.25" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="7"/>
       <c r="C33" s="62" t="s">
-        <v>216</v>
+        <v>124</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>217</v>
+        <v>125</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="G33" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="19" customHeight="1">
+    <row r="34" spans="1:7" ht="25.25" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="7"/>
       <c r="C34" s="62" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="G34" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="19" customHeight="1">
+    <row r="35" spans="1:7" ht="25.25" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="10" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>225</v>
+        <v>136</v>
       </c>
       <c r="G35" s="10">
         <v>2023</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="19" customHeight="1">
+    <row r="36" spans="1:7" ht="25.25" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="10"/>
       <c r="C36" s="65" t="s">
-        <v>226</v>
+        <v>137</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>227</v>
+        <v>138</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>9</v>
+        <v>139</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G36" s="10">
         <v>2023</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="19" customHeight="1">
+    <row r="37" spans="1:7" ht="25.25" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="10"/>
       <c r="C37" s="65" t="s">
-        <v>228</v>
+        <v>140</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>229</v>
+        <v>141</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>12</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G37" s="10">
         <v>2023</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="19" customHeight="1">
+    <row r="38" spans="1:7" ht="25.25" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="10"/>
       <c r="C38" s="65" t="s">
-        <v>230</v>
+        <v>143</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>231</v>
+        <v>144</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G38" s="10">
         <v>2024</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="19" customHeight="1">
+    <row r="39" spans="1:7" ht="25.25" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="11" t="s">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="C39" s="66" t="s">
-        <v>233</v>
+        <v>147</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="G39" s="12">
         <v>2023</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="19" customHeight="1">
+    <row r="40" spans="1:7" ht="25.25" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="11"/>
       <c r="C40" s="66" t="s">
-        <v>236</v>
+        <v>151</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>237</v>
+        <v>152</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="G40" s="12">
         <v>2024</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="19" customHeight="1">
+    <row r="41" spans="1:7" ht="25.25" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="11"/>
       <c r="C41" s="67" t="s">
-        <v>239</v>
+        <v>155</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>487</v>
+        <v>156</v>
       </c>
       <c r="E41" s="94" t="s">
-        <v>490</v>
+        <v>157</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>488</v>
+        <v>158</v>
       </c>
       <c r="G41" s="12">
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="19" customHeight="1">
+    <row r="42" spans="1:7" ht="25.25" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="11"/>
       <c r="C42" s="67" t="s">
-        <v>240</v>
+        <v>159</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="G42" s="12">
         <v>2025</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="19" customHeight="1">
+    <row r="43" spans="1:7" ht="25.25" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="16" t="s">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>245</v>
+        <v>165</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G43" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="19" customHeight="1">
+    <row r="44" spans="1:7" ht="25.25" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="16"/>
       <c r="C44" s="58" t="s">
-        <v>246</v>
+        <v>167</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>215</v>
+        <v>123</v>
       </c>
       <c r="G44" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="19" customHeight="1">
+    <row r="45" spans="1:7" ht="25.25" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="16"/>
       <c r="C45" s="57" t="s">
-        <v>248</v>
+        <v>170</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>249</v>
+        <v>171</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>19</v>
+        <v>172</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G45" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="19" customHeight="1">
+    <row r="46" spans="1:7" ht="25.25" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="16"/>
       <c r="C46" s="58" t="s">
-        <v>250</v>
+        <v>173</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>251</v>
+        <v>174</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G46" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="19" customHeight="1">
+    <row r="47" spans="1:7" ht="25.25" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="16"/>
       <c r="C47" s="57" t="s">
-        <v>252</v>
+        <v>176</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>253</v>
+        <v>177</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="G47" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="19" customHeight="1">
+    <row r="48" spans="1:7" ht="25.25" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="16"/>
       <c r="C48" s="57" t="s">
-        <v>254</v>
+        <v>179</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="G48" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="19" customHeight="1">
+    <row r="49" spans="1:7" ht="25.25" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="17" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="C49" s="68" t="s">
-        <v>258</v>
+        <v>184</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>259</v>
+        <v>185</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>23</v>
+        <v>186</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="G49" s="17">
         <v>2023</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="19" customHeight="1">
+    <row r="50" spans="1:7" ht="25.25" customHeight="1">
       <c r="A50" s="3"/>
       <c r="B50" s="17"/>
       <c r="C50" s="68" t="s">
-        <v>260</v>
+        <v>187</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>261</v>
+        <v>188</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>22</v>
+        <v>189</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="G50" s="17">
         <v>2024</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="19" customHeight="1">
+    <row r="51" spans="1:7" ht="25.25" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="17"/>
       <c r="C51" s="68" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>264</v>
+        <v>192</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>265</v>
+        <v>194</v>
       </c>
       <c r="G51" s="17">
         <v>2025</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="19" customHeight="1">
+    <row r="52" spans="1:7" ht="25.25" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="17"/>
       <c r="C52" s="68" t="s">
-        <v>266</v>
+        <v>195</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>267</v>
+        <v>196</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>24</v>
+        <v>197</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>268</v>
+        <v>198</v>
       </c>
       <c r="G52" s="17">
         <v>2025</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="14">
+    <row r="53" spans="1:7">
       <c r="A53" s="22"/>
       <c r="B53" s="26"/>
       <c r="C53" s="69" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>27</v>
+        <v>201</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>268</v>
+        <v>198</v>
       </c>
       <c r="G53" s="25">
         <v>2025</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="19" customHeight="1">
+    <row r="54" spans="1:7" ht="25.25" customHeight="1">
       <c r="A54" s="22"/>
       <c r="B54" s="20"/>
       <c r="C54" s="70" t="s">
-        <v>271</v>
+        <v>202</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>272</v>
+        <v>203</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>273</v>
+        <v>205</v>
       </c>
       <c r="G54" s="20">
         <v>2025</v>
@@ -6965,71 +6641,13 @@
       <c r="G237" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="E38" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E46" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="E6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="E5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E24" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="E53" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="E27" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="E48" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="E15" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="E4" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="E19" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="E18" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="E50" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="E32" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="E45" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="E20" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="E25" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="E39" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="E16" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="E34" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="E29" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="E2" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="E49" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="E7" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="E40" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="E30" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="E26" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="E37" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="E51" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="E31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="E41" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="E14" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="E54" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="E47" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="E10" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="E22" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="E21" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="E42" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="E23" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="E52" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="E33" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="E35" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="E17" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="E28" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="E9" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="E44" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="E3" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="E12" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="E36" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="E43" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="E13" r:id="rId52" xr:uid="{11FCC11B-99E2-6B4C-A9D4-EECA298CBFF2}"/>
-    <hyperlink ref="E11" r:id="rId53" xr:uid="{30541ACD-5F48-0E47-9B9E-C7F9A22B1B61}"/>
-  </hyperlinks>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5459C5CE-FE36-E246-AB39-6A9B23F5844F}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K256"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
@@ -7040,128 +6658,126 @@
     <col min="5" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14">
+    <row r="1" spans="1:8">
       <c r="A1" s="29" t="s">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="C1" s="80" t="s">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="G1" s="29" t="s">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="H1" s="29" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19" customHeight="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="25.25" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>274</v>
+        <v>206</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>275</v>
+        <v>207</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>90</v>
+        <v>208</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G2" s="27">
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="23" customHeight="1">
+    <row r="3" spans="1:8" ht="30.75" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" s="27"/>
       <c r="C3" s="54" t="s">
-        <v>276</v>
+        <v>209</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>277</v>
+        <v>210</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>91</v>
+        <v>211</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G3" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="14">
-      <c r="A4" s="3" t="s">
-        <v>142</v>
-      </c>
+    <row r="4" spans="1:8">
+      <c r="A4" s="3"/>
       <c r="B4" s="27"/>
       <c r="C4" s="54" t="s">
-        <v>278</v>
+        <v>212</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>279</v>
+        <v>213</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>92</v>
+        <v>214</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>188</v>
+        <v>86</v>
       </c>
       <c r="G4" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="19" customHeight="1">
+    <row r="5" spans="1:8" ht="25.25" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="27"/>
       <c r="C5" s="54" t="s">
-        <v>280</v>
+        <v>215</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>281</v>
+        <v>216</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>93</v>
+        <v>217</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G5" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19" customHeight="1">
+    <row r="6" spans="1:8" ht="25.25" customHeight="1">
       <c r="A6" s="84"/>
       <c r="B6" s="86"/>
       <c r="C6" s="90" t="s">
-        <v>485</v>
+        <v>218</v>
       </c>
       <c r="D6" s="91" t="s">
-        <v>484</v>
+        <v>219</v>
       </c>
       <c r="E6" s="93" t="s">
-        <v>486</v>
+        <v>220</v>
       </c>
       <c r="F6" s="92" t="s">
-        <v>479</v>
+        <v>17</v>
       </c>
       <c r="G6" s="86">
         <v>2026</v>
@@ -7170,296 +6786,294 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="19" customHeight="1">
+    <row r="7" spans="1:8" ht="25.25" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="27" t="s">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>282</v>
+        <v>221</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>283</v>
+        <v>222</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>284</v>
+        <v>224</v>
       </c>
       <c r="G7" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="19" customHeight="1">
+    <row r="8" spans="1:8" ht="25.25" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="27"/>
       <c r="C8" s="54" t="s">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>286</v>
+        <v>226</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G8" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="19" customHeight="1">
+    <row r="9" spans="1:8" ht="25.25" customHeight="1">
       <c r="A9" s="84"/>
       <c r="B9" s="86"/>
       <c r="C9" s="54" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>288</v>
+        <v>229</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>83</v>
+        <v>230</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G9" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="19" customHeight="1">
+    <row r="10" spans="1:8" ht="25.25" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="27"/>
       <c r="C10" s="54" t="s">
-        <v>482</v>
+        <v>231</v>
       </c>
       <c r="D10" s="87" t="s">
-        <v>480</v>
+        <v>232</v>
       </c>
       <c r="E10" s="88" t="s">
-        <v>481</v>
+        <v>233</v>
       </c>
       <c r="F10" s="89" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="G10" s="89">
         <v>2025</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="19" customHeight="1">
+    <row r="11" spans="1:8" ht="25.25" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="27" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>290</v>
+        <v>235</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>291</v>
+        <v>237</v>
       </c>
       <c r="G11" s="27">
         <v>2024</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19" customHeight="1">
+    <row r="12" spans="1:8" ht="25.25" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="27"/>
       <c r="C12" s="54" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G12" s="27">
         <v>2024</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="19" customHeight="1">
+    <row r="13" spans="1:8" ht="25.25" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="27"/>
       <c r="C13" s="54" t="s">
-        <v>294</v>
+        <v>241</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>86</v>
+        <v>243</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G13" s="27">
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="19" customHeight="1">
+    <row r="14" spans="1:8" ht="25.25" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>296</v>
+        <v>244</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>87</v>
+        <v>246</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G14" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="19" customHeight="1">
+    <row r="15" spans="1:8" ht="25.25" customHeight="1">
       <c r="A15" s="3"/>
       <c r="B15" s="16"/>
       <c r="C15" s="58" t="s">
-        <v>298</v>
+        <v>247</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>299</v>
+        <v>248</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>88</v>
+        <v>249</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G15" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="14">
+    <row r="16" spans="1:8">
       <c r="A16" s="8"/>
       <c r="B16" s="16"/>
       <c r="C16" s="57" t="s">
-        <v>301</v>
+        <v>251</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>302</v>
+        <v>252</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>102</v>
+        <v>253</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G16" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14">
-      <c r="A17" s="3" t="s">
-        <v>142</v>
-      </c>
+    <row r="17" spans="1:11">
+      <c r="A17" s="3"/>
       <c r="B17" s="16"/>
       <c r="C17" s="57" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>103</v>
+        <v>256</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>305</v>
+        <v>257</v>
       </c>
       <c r="G17" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="19" customHeight="1">
+    <row r="18" spans="1:11" ht="25.25" customHeight="1">
       <c r="A18" s="3"/>
       <c r="B18" s="16"/>
       <c r="C18" s="57" t="s">
-        <v>306</v>
+        <v>258</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>307</v>
+        <v>259</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>104</v>
+        <v>260</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>308</v>
+        <v>261</v>
       </c>
       <c r="G18" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="19" customHeight="1">
+    <row r="19" spans="1:11" ht="25.25" customHeight="1">
       <c r="A19" s="3"/>
       <c r="B19" s="16"/>
       <c r="C19" s="58" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>105</v>
+        <v>264</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="G19" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="19" customHeight="1">
+    <row r="20" spans="1:11" ht="25.25" customHeight="1">
       <c r="A20" s="84"/>
       <c r="B20" s="98"/>
       <c r="C20" s="57" t="s">
-        <v>312</v>
+        <v>266</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>313</v>
+        <v>267</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>106</v>
+        <v>268</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G20" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="19" customHeight="1">
+    <row r="21" spans="1:11" ht="25.25" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="16"/>
       <c r="C21" s="57" t="s">
-        <v>496</v>
+        <v>269</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>497</v>
+        <v>270</v>
       </c>
       <c r="E21" s="99" t="s">
-        <v>498</v>
+        <v>271</v>
       </c>
       <c r="F21" s="33" t="s">
-        <v>434</v>
+        <v>13</v>
       </c>
       <c r="G21" s="16">
         <v>2026</v>
@@ -7468,119 +7082,119 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="19" customHeight="1">
+    <row r="22" spans="1:11" ht="25.25" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="35" t="s">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>314</v>
+        <v>272</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>107</v>
+        <v>274</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G22" s="35">
         <v>2024</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="19" customHeight="1">
+    <row r="23" spans="1:11" ht="25.25" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="35"/>
       <c r="C23" s="59" t="s">
-        <v>316</v>
+        <v>275</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>108</v>
+        <v>277</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
       <c r="G23" s="35">
         <v>2025</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="19" customHeight="1">
+    <row r="24" spans="1:11" ht="25.25" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="35"/>
       <c r="C24" s="59" t="s">
-        <v>319</v>
+        <v>279</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>109</v>
+        <v>281</v>
       </c>
       <c r="F24" s="35" t="s">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="G24" s="35">
         <v>2025</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="19" customHeight="1">
+    <row r="25" spans="1:11" ht="25.25" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="1" t="s">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>322</v>
+        <v>283</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>323</v>
+        <v>284</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>94</v>
+        <v>285</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G25" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="19" customHeight="1">
+    <row r="26" spans="1:11" ht="25.25" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="1"/>
       <c r="C26" s="60" t="s">
-        <v>324</v>
+        <v>286</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>325</v>
+        <v>287</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G26" s="1">
         <v>2024</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="19" customHeight="1">
+    <row r="27" spans="1:11" ht="25.25" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="1"/>
       <c r="C27" s="61" t="s">
-        <v>326</v>
+        <v>289</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>327</v>
+        <v>290</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>96</v>
+        <v>291</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>188</v>
+        <v>86</v>
       </c>
       <c r="G27" s="1">
         <v>2024</v>
@@ -7590,20 +7204,20 @@
       <c r="J27" s="49"/>
       <c r="K27" s="49"/>
     </row>
-    <row r="28" spans="1:11" ht="19" customHeight="1">
+    <row r="28" spans="1:11" ht="25.25" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="60" t="s">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>97</v>
+        <v>294</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G28" s="1">
         <v>2025</v>
@@ -7613,409 +7227,409 @@
       <c r="J28" s="49"/>
       <c r="K28" s="49"/>
     </row>
-    <row r="29" spans="1:11" ht="19" customHeight="1">
+    <row r="29" spans="1:11" ht="25.25" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="61" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>332</v>
+        <v>298</v>
       </c>
       <c r="G29" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="19" customHeight="1">
+    <row r="30" spans="1:11" ht="25.25" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="60" t="s">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>99</v>
+        <v>301</v>
       </c>
       <c r="F30" s="48" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G30" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="19" customHeight="1">
+    <row r="31" spans="1:11" ht="25.25" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="1"/>
       <c r="C31" s="60" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>100</v>
+        <v>304</v>
       </c>
       <c r="F31" s="48" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G31" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="19" customHeight="1">
+    <row r="32" spans="1:11" ht="25.25" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>208</v>
+        <v>114</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>209</v>
+        <v>115</v>
       </c>
       <c r="C32" s="62" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>101</v>
+        <v>307</v>
       </c>
       <c r="F32" s="40" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G32" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="19" customHeight="1">
+    <row r="33" spans="1:8" ht="25.25" customHeight="1">
       <c r="A33" s="8"/>
       <c r="B33" s="7"/>
       <c r="C33" s="62" t="s">
-        <v>339</v>
+        <v>308</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>57</v>
+        <v>310</v>
       </c>
       <c r="F33" s="40" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G33" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="19" customHeight="1">
+    <row r="34" spans="1:8" ht="25.25" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="7"/>
       <c r="C34" s="62" t="s">
-        <v>341</v>
+        <v>311</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>58</v>
+        <v>313</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>215</v>
+        <v>123</v>
       </c>
       <c r="G34" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="19" customHeight="1">
+    <row r="35" spans="1:8" ht="25.25" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="7"/>
       <c r="C35" s="63" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>59</v>
+        <v>316</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G35" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="19" customHeight="1">
+    <row r="36" spans="1:8" ht="25.25" customHeight="1">
       <c r="A36" s="84"/>
       <c r="B36" s="85"/>
       <c r="C36" s="73" t="s">
-        <v>345</v>
+        <v>317</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>346</v>
+        <v>318</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>60</v>
+        <v>319</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>273</v>
+        <v>205</v>
       </c>
       <c r="G36" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="19" customHeight="1">
+    <row r="37" spans="1:8" ht="25.25" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="7"/>
       <c r="C37" s="73" t="s">
-        <v>476</v>
+        <v>320</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>477</v>
+        <v>321</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>478</v>
+        <v>322</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>479</v>
+        <v>17</v>
       </c>
       <c r="G37" s="7">
         <v>2026</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="19" customHeight="1">
+    <row r="38" spans="1:8" ht="25.25" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="10" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="C38" s="65" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>61</v>
+        <v>325</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="G38" s="10">
         <v>2023</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="19" customHeight="1">
+    <row r="39" spans="1:8" ht="25.25" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="10"/>
       <c r="C39" s="65" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>62</v>
+        <v>328</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G39" s="10">
         <v>2024</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="19" customHeight="1">
+    <row r="40" spans="1:8" ht="25.25" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="10"/>
       <c r="C40" s="65" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>63</v>
+        <v>331</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>215</v>
+        <v>123</v>
       </c>
       <c r="G40" s="10">
         <v>2024</v>
       </c>
       <c r="H40" s="41"/>
     </row>
-    <row r="41" spans="1:8" ht="19" customHeight="1">
+    <row r="41" spans="1:8" ht="25.25" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="10"/>
       <c r="C41" s="65" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>64</v>
+        <v>334</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="G41" s="10">
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="19" customHeight="1">
+    <row r="42" spans="1:8" ht="25.25" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="10"/>
       <c r="C42" s="65" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>110</v>
+        <v>338</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="G42" s="10">
         <v>2025</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="19" customHeight="1">
+    <row r="43" spans="1:8" ht="25.25" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="10"/>
       <c r="C43" s="64" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>483</v>
+        <v>340</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>111</v>
+        <v>341</v>
       </c>
       <c r="F43" s="36" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G43" s="10">
         <v>2025</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="19" customHeight="1">
+    <row r="44" spans="1:8" ht="25.25" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="10"/>
       <c r="C44" s="65" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>51</v>
+        <v>344</v>
       </c>
       <c r="F44" s="36" t="s">
-        <v>479</v>
+        <v>17</v>
       </c>
       <c r="G44" s="10">
         <v>2026</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="19" customHeight="1">
+    <row r="45" spans="1:8" ht="25.25" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="11" t="s">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="C45" s="74" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>52</v>
+        <v>347</v>
       </c>
       <c r="F45" s="39" t="s">
-        <v>273</v>
+        <v>205</v>
       </c>
       <c r="G45" s="11">
         <v>2024</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="19" customHeight="1">
+    <row r="46" spans="1:8" ht="25.25" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="11"/>
       <c r="C46" s="75" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>53</v>
+        <v>350</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G46" s="11">
         <v>2024</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="19" customHeight="1">
+    <row r="47" spans="1:8" ht="25.25" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="11"/>
       <c r="C47" s="74" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>54</v>
+        <v>353</v>
       </c>
       <c r="F47" s="39" t="s">
-        <v>273</v>
+        <v>205</v>
       </c>
       <c r="G47" s="11">
         <v>2025</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="19" customHeight="1">
+    <row r="48" spans="1:8" ht="25.25" customHeight="1">
       <c r="A48" s="84"/>
       <c r="B48" s="95"/>
       <c r="C48" s="75" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>55</v>
+        <v>356</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="G48" s="11">
         <v>2025</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="19" customHeight="1">
+    <row r="49" spans="1:8" ht="25.25" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="11"/>
       <c r="C49" s="75" t="s">
-        <v>492</v>
+        <v>357</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>493</v>
+        <v>358</v>
       </c>
       <c r="E49" s="96" t="s">
-        <v>494</v>
+        <v>359</v>
       </c>
       <c r="F49" s="39" t="s">
-        <v>479</v>
+        <v>17</v>
       </c>
       <c r="G49" s="11">
         <v>2026</v>
@@ -8024,183 +7638,183 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="19" customHeight="1">
+    <row r="50" spans="1:8" ht="25.25" customHeight="1">
       <c r="A50" s="3"/>
       <c r="B50" s="16" t="s">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="C50" s="58" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>56</v>
+        <v>362</v>
       </c>
       <c r="F50" s="33" t="s">
-        <v>475</v>
+        <v>136</v>
       </c>
       <c r="G50" s="16">
         <v>2023</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="19" customHeight="1">
+    <row r="51" spans="1:8" ht="25.25" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="16"/>
       <c r="C51" s="58" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>73</v>
+        <v>365</v>
       </c>
       <c r="F51" s="33" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="G51" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="19" customHeight="1">
+    <row r="52" spans="1:8" ht="25.25" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="16"/>
       <c r="C52" s="57" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>74</v>
+        <v>368</v>
       </c>
       <c r="F52" s="33" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G52" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="19" customHeight="1">
+    <row r="53" spans="1:8" ht="25.25" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="16"/>
       <c r="C53" s="58" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>75</v>
+        <v>371</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>215</v>
+        <v>123</v>
       </c>
       <c r="G53" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="19" customHeight="1">
+    <row r="54" spans="1:8" ht="25.25" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="16"/>
       <c r="C54" s="58" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>76</v>
+        <v>374</v>
       </c>
       <c r="F54" s="33" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G54" s="16">
         <v>2024</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="19" customHeight="1">
+    <row r="55" spans="1:8" ht="25.25" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="16"/>
       <c r="C55" s="58" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>77</v>
+        <v>377</v>
       </c>
       <c r="F55" s="33" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G55" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="19" customHeight="1">
+    <row r="56" spans="1:8" ht="25.25" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="16"/>
       <c r="C56" s="57" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="G56" s="16">
         <v>2025</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="19" customHeight="1">
+    <row r="57" spans="1:8" ht="25.25" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="16"/>
       <c r="C57" s="57" t="s">
+        <v>381</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="E57" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="D57" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="E57" s="15" t="s">
-        <v>79</v>
-      </c>
       <c r="F57" s="33" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G57" s="33">
         <v>2025</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="19" customHeight="1">
+    <row r="58" spans="1:8" ht="25.25" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="16"/>
       <c r="C58" s="57" t="s">
+        <v>384</v>
+      </c>
+      <c r="D58" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="E58" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="E58" s="15" t="s">
-        <v>80</v>
-      </c>
       <c r="F58" s="33" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G58" s="33">
         <v>2025</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="19" customHeight="1">
+    <row r="59" spans="1:8" ht="25.25" customHeight="1">
       <c r="A59" s="42"/>
       <c r="B59" s="17" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="C59" s="68" t="s">
         <v>387</v>
@@ -8209,168 +7823,168 @@
         <v>388</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>65</v>
+        <v>389</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="G59" s="43">
         <v>2024</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="19" customHeight="1">
+    <row r="60" spans="1:8" ht="25.25" customHeight="1">
       <c r="A60" s="42"/>
       <c r="B60" s="43"/>
       <c r="C60" s="76" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>66</v>
+        <v>392</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G60" s="43">
         <v>2024</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="14">
+    <row r="61" spans="1:8">
       <c r="A61" s="42"/>
       <c r="B61" s="43"/>
       <c r="C61" s="76" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>67</v>
+        <v>396</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="G61" s="43">
         <v>2024</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="19" customHeight="1">
+    <row r="62" spans="1:8" ht="25.25" customHeight="1">
       <c r="A62" s="42"/>
       <c r="B62" s="43"/>
       <c r="C62" s="68" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>68</v>
+        <v>399</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G62" s="43">
         <v>2025</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="19" customHeight="1">
+    <row r="63" spans="1:8" ht="25.25" customHeight="1">
       <c r="A63" s="42"/>
       <c r="B63" s="43"/>
       <c r="C63" s="68" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>69</v>
+        <v>402</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="G63" s="43">
         <v>2025</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="14">
+    <row r="64" spans="1:8">
       <c r="A64" s="42"/>
       <c r="B64" s="43"/>
       <c r="C64" s="76" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>70</v>
+        <v>405</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="G64" s="43">
         <v>2025</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="14">
+    <row r="65" spans="1:7">
       <c r="A65" s="42"/>
       <c r="B65" s="43"/>
       <c r="C65" s="76" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>71</v>
+        <v>408</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="G65" s="43">
         <v>2025</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="14">
+    <row r="66" spans="1:7">
       <c r="A66" s="42"/>
       <c r="B66" s="43"/>
       <c r="C66" s="76" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>72</v>
+        <v>411</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="G66" s="43">
         <v>2025</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="14">
+    <row r="67" spans="1:7">
       <c r="A67" s="42"/>
       <c r="B67" s="43"/>
       <c r="C67" s="76" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>89</v>
+        <v>414</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="G67" s="43">
         <v>2025</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="17">
+    <row r="68" spans="1:7" ht="16">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="72"/>
@@ -10072,83 +9686,13 @@
       <c r="G256" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="E64" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="E19" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="E61" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="E47" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="E23" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="E25" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="E26" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="E14" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="E56" r:id="rId9" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="E28" r:id="rId10" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="E30" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="E52" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="E46" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="E15" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="E62" r:id="rId15" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="E59" r:id="rId16" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="E17" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="E65" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="E53" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="E27" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="E41" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="E45" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="E38" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="E5" r:id="rId24" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="E44" r:id="rId25" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="E13" r:id="rId26" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="E7" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="E4" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="E66" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="E63" r:id="rId30" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="E58" r:id="rId31" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="E34" r:id="rId32" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="E54" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="E2" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="E16" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="E55" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="E24" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="E31" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="E11" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="E43" r:id="rId40" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="E33" r:id="rId41" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="E18" r:id="rId42" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="E3" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="E50" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="E12" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="E57" r:id="rId46" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="E8" r:id="rId47" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="E51" r:id="rId48" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="E42" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="E22" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="E60" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="E35" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="E40" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
-    <hyperlink ref="E39" r:id="rId54" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
-    <hyperlink ref="E32" r:id="rId55" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
-    <hyperlink ref="E67" r:id="rId56" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
-    <hyperlink ref="E29" r:id="rId57" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
-    <hyperlink ref="E36" r:id="rId58" xr:uid="{7EC1841A-D2E4-4D40-85F8-574AF7C9ED0F}"/>
-    <hyperlink ref="E9" r:id="rId59" xr:uid="{5F14C7A6-B6D6-9542-8B33-155349E77E8F}"/>
-    <hyperlink ref="E10" r:id="rId60" xr:uid="{AF98066F-1603-B94A-BA89-552597EAD77F}"/>
-    <hyperlink ref="E6" r:id="rId61" xr:uid="{C9881E59-5194-2E4A-BA83-759370DAD6ED}"/>
-    <hyperlink ref="E48" r:id="rId62" xr:uid="{5BC41198-863A-4B49-A628-ACE02D2FCC04}"/>
-    <hyperlink ref="E49" r:id="rId63" xr:uid="{C7D2FA05-774D-B74F-BB11-AA780E335549}"/>
-    <hyperlink ref="E20" r:id="rId64" xr:uid="{7830403C-4CB8-1F42-AB6B-8837083A1F83}"/>
-    <hyperlink ref="E21" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-  </hyperlinks>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1CC9A4-47DF-304A-A7AF-069274959BAD}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
@@ -10160,28 +9704,28 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="106" t="s">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="B1" s="106" t="s">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="C1" s="106" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="D1" s="106" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="E1" s="106" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="F1" s="106" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="G1" s="106" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19" customHeight="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25.25" customHeight="1">
       <c r="A2" s="106"/>
       <c r="B2" s="106"/>
       <c r="C2" s="106"/>
@@ -10195,296 +9739,300 @@
         <v>2026</v>
       </c>
       <c r="B3" s="79" t="s">
-        <v>504</v>
+        <v>451</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>506</v>
+        <v>452</v>
       </c>
       <c r="D3" s="105" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="E3" s="53" t="s">
-        <v>513</v>
+        <v>454</v>
       </c>
       <c r="F3" s="52" t="s">
-        <v>505</v>
+        <v>455</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14">
-      <c r="A4" s="37">
+    <row r="4" spans="1:7">
+      <c r="A4" s="100">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="102" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4" s="103" t="s">
+        <v>465</v>
+      </c>
+      <c r="D4" s="104" t="s">
+        <v>466</v>
+      </c>
+      <c r="E4" s="101" t="s">
+        <v>335</v>
+      </c>
+      <c r="F4" s="103" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="37">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="79" t="s">
+        <v>456</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="25.25" customHeight="1">
+      <c r="A6" s="37">
         <v>2025</v>
       </c>
-      <c r="B4" s="79" t="s">
-        <v>407</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="53" t="s">
-        <v>434</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19" customHeight="1">
-      <c r="A5" s="37">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="77" t="s">
-        <v>410</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>434</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19" customHeight="1">
-      <c r="A6" s="100">
+      <c r="B6" s="77" t="s">
+        <v>460</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="37">
         <v>2026</v>
       </c>
-      <c r="B6" s="102" t="s">
-        <v>503</v>
-      </c>
-      <c r="C6" s="103" t="s">
-        <v>502</v>
-      </c>
-      <c r="D6" s="104" t="s">
-        <v>501</v>
-      </c>
-      <c r="E6" s="101" t="s">
-        <v>499</v>
-      </c>
-      <c r="F6" s="103" t="s">
-        <v>500</v>
-      </c>
-      <c r="G6">
+      <c r="B7" s="77" t="s">
+        <v>467</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14">
-      <c r="A7" s="37">
-        <v>2025</v>
-      </c>
-      <c r="B7" s="77" t="s">
-        <v>413</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7" s="53" t="s">
-        <v>472</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="14">
+    <row r="8" spans="1:7">
       <c r="A8" s="37">
         <v>2025</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>415</v>
+        <v>471</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>416</v>
+        <v>472</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>120</v>
+        <v>473</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>417</v>
+        <v>237</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="14">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="37">
         <v>2025</v>
       </c>
       <c r="B9" s="78" t="s">
-        <v>418</v>
+        <v>474</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>419</v>
+        <v>475</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>123</v>
+        <v>476</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>435</v>
+        <v>477</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="14">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="37">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="77" t="s">
+        <v>478</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="37">
         <v>2024</v>
       </c>
-      <c r="B10" s="77" t="s">
-        <v>420</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="14">
-      <c r="A11" s="37"/>
       <c r="B11" s="77" t="s">
-        <v>423</v>
+        <v>482</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>433</v>
+        <v>483</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="37"/>
+        <v>484</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>485</v>
+      </c>
       <c r="F11" s="52" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19" customHeight="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="25.25" customHeight="1">
       <c r="A12" s="37"/>
       <c r="B12" s="77" t="s">
-        <v>424</v>
+        <v>487</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>112</v>
+        <v>489</v>
       </c>
       <c r="E12" s="37"/>
       <c r="F12" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19" customHeight="1">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="25.25" customHeight="1">
       <c r="A13" s="37"/>
       <c r="B13" s="78" t="s">
-        <v>126</v>
+        <v>491</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>115</v>
+        <v>492</v>
       </c>
       <c r="E13" s="37"/>
       <c r="F13" s="5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19" customHeight="1">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="25.25" customHeight="1">
       <c r="A14" s="37"/>
       <c r="B14" s="78" t="s">
-        <v>427</v>
+        <v>2</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>114</v>
+        <v>494</v>
       </c>
       <c r="E14" s="37"/>
       <c r="F14" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19" customHeight="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="25.25" customHeight="1">
       <c r="A15" s="37"/>
       <c r="B15" s="77" t="s">
-        <v>429</v>
+        <v>496</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>117</v>
+        <v>497</v>
       </c>
       <c r="E15" s="37"/>
       <c r="F15" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19" customHeight="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="25.25" customHeight="1">
       <c r="A16" s="37"/>
       <c r="B16" s="78" t="s">
-        <v>431</v>
+        <v>499</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>116</v>
+        <v>500</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="19" customHeight="1">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="25.25" customHeight="1">
       <c r="A17" s="37"/>
       <c r="B17" s="37" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="E17" s="37"/>
       <c r="F17" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="19" customHeight="1">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="25.25" customHeight="1">
       <c r="A18" s="37"/>
       <c r="B18" s="53" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -10492,11 +10040,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="B19" s="37" t="s">
+        <v>508</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>509</v>
+      </c>
       <c r="E19" s="37"/>
-      <c r="F19" s="5"/>
+      <c r="F19" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="37"/>
@@ -11980,29 +11539,13 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="D10" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="D11" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="D14" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="D16" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="D8" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="D12" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="D13" r:id="rId10" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
-    <hyperlink ref="D15" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
-    <hyperlink ref="D9" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
-    <hyperlink ref="D6" r:id="rId13" xr:uid="{8F01A46B-F312-6944-B099-6C2A96D521DA}"/>
-    <hyperlink ref="D3" r:id="rId14" xr:uid="{4286F07A-CF69-BD44-AA40-BFEEC2472490}"/>
-  </hyperlinks>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF57CB64-0143-634E-B2B9-D0257CE1E416}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
@@ -12011,19 +11554,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="81" t="s">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="B1" s="81" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="C1" s="81" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="D1" s="81" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="E1" s="81" t="s">
-        <v>491</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -12031,13 +11574,13 @@
         <v>2025</v>
       </c>
       <c r="B2" s="82" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="C2" s="83" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="D2" s="82" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -12045,13 +11588,13 @@
         <v>2025</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="C3" s="83" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="D3" s="82" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -12059,13 +11602,13 @@
         <v>2025</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="C4" s="83" t="s">
-        <v>446</v>
+        <v>423</v>
       </c>
       <c r="D4" s="82" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -12073,13 +11616,13 @@
         <v>2025</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="C5" s="83" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="D5" s="82" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -12087,13 +11630,13 @@
         <v>2025</v>
       </c>
       <c r="B6" s="82" t="s">
-        <v>473</v>
+        <v>426</v>
       </c>
       <c r="C6" s="83" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="D6" s="82" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -12101,13 +11644,13 @@
         <v>2025</v>
       </c>
       <c r="B7" s="82" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="C7" s="83" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="D7" s="82" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -12115,13 +11658,13 @@
         <v>2025</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="C8" s="83" t="s">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="D8" s="82" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -12129,13 +11672,13 @@
         <v>2025</v>
       </c>
       <c r="B9" s="82" t="s">
-        <v>474</v>
+        <v>432</v>
       </c>
       <c r="C9" s="83" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="D9" s="82" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -12143,13 +11686,13 @@
         <v>2025</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="C10" s="83" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="D10" s="82" t="s">
-        <v>458</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -12157,13 +11700,13 @@
         <v>2025</v>
       </c>
       <c r="B11" s="82" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="C11" s="83" t="s">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="D11" s="82" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -12171,13 +11714,13 @@
         <v>2024</v>
       </c>
       <c r="B12" s="82" t="s">
-        <v>462</v>
+        <v>441</v>
       </c>
       <c r="C12" s="83" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="D12" s="82" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -12185,13 +11728,13 @@
         <v>2024</v>
       </c>
       <c r="B13" s="82" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="C13" s="83" t="s">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="D13" s="82" t="s">
-        <v>273</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -12199,13 +11742,13 @@
         <v>2023</v>
       </c>
       <c r="B14" s="82" t="s">
-        <v>466</v>
+        <v>445</v>
       </c>
       <c r="C14" s="83" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="D14" s="82" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -12213,13 +11756,13 @@
         <v>2023</v>
       </c>
       <c r="B15" s="82" t="s">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="C15" s="83" t="s">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="D15" s="82" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -12227,34 +11770,17 @@
         <v>2023</v>
       </c>
       <c r="B16" s="82" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="C16" s="83" t="s">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="D16" s="82" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{B2A53827-C15F-0548-95CE-E328D91FA31F}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{65DED945-1FCA-204C-9A78-128107C30375}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{9CB2BFBA-5BED-F24A-8133-B15C7B58E116}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{FC722738-4636-D445-A0BD-26A1D45477DD}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{259C37F5-23CE-494D-94F4-EE17FB3EE14F}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{791F22E6-3ABA-E148-A84F-CA6CF6D8758B}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{AD2B3145-F24F-4946-B77E-E7B37B0CAB68}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{B226C81E-3A01-BD49-95FE-6F282FB81697}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{9FA663DA-3771-BA45-B80C-FE35FC6E6EA5}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{F3B67895-25B9-854F-91B7-C2BA267A9D7B}"/>
-    <hyperlink ref="C12" r:id="rId11" xr:uid="{E3AF1F7D-C0C7-534E-9AB0-D35C8744AB7D}"/>
-    <hyperlink ref="C13" r:id="rId12" xr:uid="{5EABC8A9-938F-6E4A-A0F5-B299C6DEE5DE}"/>
-    <hyperlink ref="C14" r:id="rId13" xr:uid="{2D76FE84-9E11-944C-86A6-3D96303DF5B5}"/>
-    <hyperlink ref="C15" r:id="rId14" xr:uid="{6DEE2295-A14C-F143-9FC3-FC2CCB966FB7}"/>
-    <hyperlink ref="C16" r:id="rId15" xr:uid="{1DB0493C-F001-4845-883F-251822557CC1}"/>
-  </hyperlinks>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/paper_list.xlsx
+++ b/src/paper_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yizhang/Desktop/Data Agents Survey/awesome-data-agents/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B5EACC-DC80-FB47-A5F5-371B799325DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E48A0C-52E7-8B40-8E73-2E0BB8420B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="46080" windowHeight="25420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="513">
   <si>
     <t>Category</t>
   </si>
@@ -2416,12 +2416,6 @@
     <t>AgenticData</t>
   </si>
   <si>
-    <t>AgenticData: An Agentic Data Analytics System for Heterogeneous Data</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/pdf/2508.05002</t>
-  </si>
-  <si>
     <t>Tsinghua University</t>
   </si>
   <si>
@@ -2548,22 +2542,42 @@
     <t>Xata</t>
   </si>
   <si>
-    <t>Julius.ai</t>
-  </si>
-  <si>
-    <t>https://julius.ai/</t>
-  </si>
-  <si>
-    <t>Julis</t>
-  </si>
-  <si>
-    <t>Bayeslab.ai</t>
-  </si>
-  <si>
-    <t>https://bayeslab.ai/</t>
-  </si>
-  <si>
-    <t>Bayeslab</t>
+    <t>SQLConductor</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQLConductor: Search-to-Policy Learning for Step-wise Text-to-SQL Orchestration</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2606.23537</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>AgenticData: A Multi-Agent based Data Analytics System for Heterogeneous Data</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>EvoDS: Self-Evolving Autonomous Data Science Agent with Skill Learning and Context Management</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>EvoDS</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2606.03841</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>KDD</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKUST(GZ)</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2508.05002v2</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3462,7 +3476,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3784,6 +3798,15 @@
     <xf numFmtId="0" fontId="6" fillId="56" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6648,7 +6671,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K256"/>
+  <dimension ref="A1:K257"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -7520,8 +7543,8 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="25.25" customHeight="1">
-      <c r="A44" s="3"/>
-      <c r="B44" s="10"/>
+      <c r="A44" s="84"/>
+      <c r="B44" s="107"/>
       <c r="C44" s="65" t="s">
         <v>342</v>
       </c>
@@ -7540,39 +7563,42 @@
     </row>
     <row r="45" spans="1:8" ht="25.25" customHeight="1">
       <c r="A45" s="3"/>
-      <c r="B45" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C45" s="74" t="s">
-        <v>345</v>
-      </c>
-      <c r="D45" s="38" t="s">
-        <v>346</v>
-      </c>
-      <c r="E45" s="38" t="s">
-        <v>347</v>
-      </c>
-      <c r="F45" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="G45" s="11">
-        <v>2024</v>
+      <c r="B45" s="10"/>
+      <c r="C45" s="108" t="s">
+        <v>503</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="E45" s="109" t="s">
+        <v>505</v>
+      </c>
+      <c r="F45" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="10">
+        <v>2026</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="25.25" customHeight="1">
       <c r="A46" s="3"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="75" t="s">
-        <v>348</v>
+      <c r="B46" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C46" s="74" t="s">
+        <v>345</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>90</v>
+        <v>205</v>
       </c>
       <c r="G46" s="11">
         <v>2024</v>
@@ -7581,117 +7607,117 @@
     <row r="47" spans="1:8" ht="25.25" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="11"/>
-      <c r="C47" s="74" t="s">
+      <c r="C47" s="75" t="s">
+        <v>348</v>
+      </c>
+      <c r="D47" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="E47" s="38" t="s">
+        <v>350</v>
+      </c>
+      <c r="F47" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="G47" s="11">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="25.25" customHeight="1">
+      <c r="A48" s="3"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="74" t="s">
         <v>351</v>
       </c>
-      <c r="D47" s="38" t="s">
+      <c r="D48" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="E47" s="38" t="s">
+      <c r="E48" s="38" t="s">
         <v>353</v>
       </c>
-      <c r="F47" s="39" t="s">
+      <c r="F48" s="39" t="s">
         <v>205</v>
-      </c>
-      <c r="G47" s="11">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="25.25" customHeight="1">
-      <c r="A48" s="84"/>
-      <c r="B48" s="95"/>
-      <c r="C48" s="75" t="s">
-        <v>354</v>
-      </c>
-      <c r="D48" s="38" t="s">
-        <v>355</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>356</v>
-      </c>
-      <c r="F48" s="39" t="s">
-        <v>154</v>
       </c>
       <c r="G48" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="25.25" customHeight="1">
-      <c r="A49" s="3"/>
-      <c r="B49" s="11"/>
+      <c r="A49" s="84"/>
+      <c r="B49" s="95"/>
       <c r="C49" s="75" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="E49" s="96" t="s">
-        <v>359</v>
+        <v>355</v>
+      </c>
+      <c r="E49" s="38" t="s">
+        <v>356</v>
       </c>
       <c r="F49" s="39" t="s">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="G49" s="11">
-        <v>2026</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="25.25" customHeight="1">
       <c r="A50" s="3"/>
-      <c r="B50" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="C50" s="58" t="s">
-        <v>360</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>361</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="F50" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="G50" s="16">
-        <v>2023</v>
+      <c r="B50" s="11"/>
+      <c r="C50" s="75" t="s">
+        <v>357</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="E50" s="96" t="s">
+        <v>359</v>
+      </c>
+      <c r="F50" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" s="11">
+        <v>2026</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="25.25" customHeight="1">
       <c r="A51" s="3"/>
-      <c r="B51" s="16"/>
+      <c r="B51" s="16" t="s">
+        <v>163</v>
+      </c>
       <c r="C51" s="58" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F51" s="33" t="s">
-        <v>335</v>
+        <v>136</v>
       </c>
       <c r="G51" s="16">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="25.25" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="16"/>
-      <c r="C52" s="57" t="s">
-        <v>366</v>
+      <c r="C52" s="58" t="s">
+        <v>363</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F52" s="33" t="s">
-        <v>90</v>
+        <v>335</v>
       </c>
       <c r="G52" s="16">
         <v>2024</v>
@@ -7700,17 +7726,17 @@
     <row r="53" spans="1:8" ht="25.25" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="16"/>
-      <c r="C53" s="58" t="s">
-        <v>369</v>
+      <c r="C53" s="57" t="s">
+        <v>366</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="G53" s="16">
         <v>2024</v>
@@ -7720,16 +7746,16 @@
       <c r="A54" s="3"/>
       <c r="B54" s="16"/>
       <c r="C54" s="58" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F54" s="33" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="G54" s="16">
         <v>2024</v>
@@ -7739,32 +7765,32 @@
       <c r="A55" s="3"/>
       <c r="B55" s="16"/>
       <c r="C55" s="58" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F55" s="33" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="G55" s="16">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="25.25" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="16"/>
-      <c r="C56" s="57" t="s">
-        <v>378</v>
+      <c r="C56" s="58" t="s">
+        <v>375</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F56" s="33" t="s">
         <v>25</v>
@@ -7777,18 +7803,18 @@
       <c r="A57" s="3"/>
       <c r="B57" s="16"/>
       <c r="C57" s="57" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="33">
+        <v>25</v>
+      </c>
+      <c r="G57" s="16">
         <v>2025</v>
       </c>
     </row>
@@ -7796,13 +7822,13 @@
       <c r="A58" s="3"/>
       <c r="B58" s="16"/>
       <c r="C58" s="57" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F58" s="33" t="s">
         <v>13</v>
@@ -7812,94 +7838,94 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="25.25" customHeight="1">
-      <c r="A59" s="42"/>
-      <c r="B59" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C59" s="68" t="s">
-        <v>387</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="E59" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="F59" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="G59" s="43">
-        <v>2024</v>
+      <c r="A59" s="3"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="57" t="s">
+        <v>384</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="F59" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="33">
+        <v>2025</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="25.25" customHeight="1">
       <c r="A60" s="42"/>
-      <c r="B60" s="43"/>
-      <c r="C60" s="76" t="s">
-        <v>390</v>
+      <c r="B60" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" s="68" t="s">
+        <v>387</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>392</v>
-      </c>
-      <c r="F60" s="25" t="s">
-        <v>393</v>
+        <v>389</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>90</v>
       </c>
       <c r="G60" s="43">
         <v>2024</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" ht="25.25" customHeight="1">
       <c r="A61" s="42"/>
       <c r="B61" s="43"/>
       <c r="C61" s="76" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>190</v>
+        <v>393</v>
       </c>
       <c r="G61" s="43">
         <v>2024</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="25.25" customHeight="1">
+    <row r="62" spans="1:8">
       <c r="A62" s="42"/>
       <c r="B62" s="43"/>
-      <c r="C62" s="68" t="s">
-        <v>397</v>
+      <c r="C62" s="76" t="s">
+        <v>394</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="G62" s="43">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="25.25" customHeight="1">
       <c r="A63" s="42"/>
       <c r="B63" s="43"/>
       <c r="C63" s="68" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F63" s="25" t="s">
         <v>13</v>
@@ -7908,20 +7934,20 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" ht="25.25" customHeight="1">
       <c r="A64" s="42"/>
       <c r="B64" s="43"/>
-      <c r="C64" s="76" t="s">
-        <v>403</v>
+      <c r="C64" s="68" t="s">
+        <v>400</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="G64" s="43">
         <v>2025</v>
@@ -7931,16 +7957,16 @@
       <c r="A65" s="42"/>
       <c r="B65" s="43"/>
       <c r="C65" s="76" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="G65" s="43">
         <v>2025</v>
@@ -7950,16 +7976,16 @@
       <c r="A66" s="42"/>
       <c r="B66" s="43"/>
       <c r="C66" s="76" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="G66" s="43">
         <v>2025</v>
@@ -7969,38 +7995,48 @@
       <c r="A67" s="42"/>
       <c r="B67" s="43"/>
       <c r="C67" s="76" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="G67" s="43">
         <v>2025</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="44"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="4"/>
-    </row>
-    <row r="69" spans="1:7">
+    <row r="68" spans="1:7">
+      <c r="A68" s="42"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="76" t="s">
+        <v>412</v>
+      </c>
+      <c r="D68" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="E68" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="F68" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="G68" s="43">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="72"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="45"/>
-      <c r="G69" s="47"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="4"/>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="4"/>
@@ -8042,10 +8078,10 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="72"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="4"/>
+      <c r="D74" s="46"/>
+      <c r="E74" s="46"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="47"/>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="4"/>
@@ -9685,15 +9721,27 @@
       <c r="F256" s="37"/>
       <c r="G256" s="4"/>
     </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="4"/>
+      <c r="B257" s="4"/>
+      <c r="C257" s="72"/>
+      <c r="D257" s="5"/>
+      <c r="E257" s="5"/>
+      <c r="F257" s="37"/>
+      <c r="G257" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E45" r:id="rId1" xr:uid="{9FD907D0-C38C-7440-90E0-75B8454D2F05}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G203"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -9762,13 +9810,13 @@
         <v>2026</v>
       </c>
       <c r="B4" s="102" t="s">
+        <v>462</v>
+      </c>
+      <c r="C4" s="103" t="s">
+        <v>463</v>
+      </c>
+      <c r="D4" s="104" t="s">
         <v>464</v>
-      </c>
-      <c r="C4" s="103" t="s">
-        <v>465</v>
-      </c>
-      <c r="D4" s="104" t="s">
-        <v>466</v>
       </c>
       <c r="E4" s="101" t="s">
         <v>335</v>
@@ -9802,42 +9850,42 @@
     </row>
     <row r="6" spans="1:7" ht="25.25" customHeight="1">
       <c r="A6" s="37">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B6" s="77" t="s">
         <v>460</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>462</v>
+      <c r="C6" s="52" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" s="105" t="s">
+        <v>512</v>
       </c>
       <c r="E6" s="53" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="37">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="25.25" customHeight="1">
+      <c r="A7" s="100">
         <v>2026</v>
       </c>
-      <c r="B7" s="77" t="s">
-        <v>467</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="E7" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>470</v>
+      <c r="B7" s="102" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>507</v>
+      </c>
+      <c r="D7" s="104" t="s">
+        <v>509</v>
+      </c>
+      <c r="E7" s="101" t="s">
+        <v>510</v>
+      </c>
+      <c r="F7" s="103" t="s">
+        <v>511</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -9845,219 +9893,212 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="37">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>237</v>
+        <v>467</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>123</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>463</v>
+        <v>468</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="37">
         <v>2025</v>
       </c>
-      <c r="B9" s="78" t="s">
-        <v>474</v>
+      <c r="B9" s="77" t="s">
+        <v>469</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>477</v>
-      </c>
-      <c r="F9" s="52" t="s">
-        <v>463</v>
+        <v>471</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="37">
         <v>2025</v>
       </c>
-      <c r="B10" s="77" t="s">
-        <v>478</v>
+      <c r="B10" s="78" t="s">
+        <v>472</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>481</v>
+        <v>475</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="37">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="77" t="s">
+        <v>476</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="37">
         <v>2024</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B12" s="77" t="s">
+        <v>480</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>481</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="E12" s="37" t="s">
         <v>483</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="F12" s="52" t="s">
         <v>484</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>485</v>
-      </c>
-      <c r="F11" s="52" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="25.25" customHeight="1">
-      <c r="A12" s="37"/>
-      <c r="B12" s="77" t="s">
-        <v>487</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>488</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="E12" s="37"/>
-      <c r="F12" s="5" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="25.25" customHeight="1">
       <c r="A13" s="37"/>
-      <c r="B13" s="78" t="s">
-        <v>491</v>
+      <c r="B13" s="77" t="s">
+        <v>485</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="E13" s="37"/>
       <c r="F13" s="5" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="25.25" customHeight="1">
       <c r="A14" s="37"/>
       <c r="B14" s="78" t="s">
-        <v>2</v>
+        <v>489</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E14" s="37"/>
       <c r="F14" s="5" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="25.25" customHeight="1">
       <c r="A15" s="37"/>
-      <c r="B15" s="77" t="s">
-        <v>496</v>
+      <c r="B15" s="78" t="s">
+        <v>2</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E15" s="37"/>
       <c r="F15" s="5" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="25.25" customHeight="1">
       <c r="A16" s="37"/>
-      <c r="B16" s="78" t="s">
-        <v>499</v>
+      <c r="B16" s="77" t="s">
+        <v>494</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="25.25" customHeight="1">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="25.25" customHeight="1">
       <c r="A17" s="37"/>
-      <c r="B17" s="37" t="s">
-        <v>502</v>
+      <c r="B17" s="78" t="s">
+        <v>497</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="E17" s="37"/>
       <c r="F17" s="5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="25.25" customHeight="1">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="25.25" customHeight="1">
       <c r="A18" s="37"/>
-      <c r="B18" s="53" t="s">
-        <v>505</v>
+      <c r="B18" s="37" t="s">
+        <v>500</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="37"/>
-      <c r="B19" s="37" t="s">
-        <v>508</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>509</v>
-      </c>
+      <c r="B19" s="37"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="37"/>
-      <c r="F19" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="37"/>
       <c r="B20" s="37"/>
       <c r="C20" s="5"/>
@@ -10065,7 +10106,7 @@
       <c r="E20" s="37"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:6">
       <c r="A21" s="37"/>
       <c r="B21" s="37"/>
       <c r="C21" s="5"/>
@@ -10073,7 +10114,7 @@
       <c r="E21" s="37"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:6">
       <c r="A22" s="37"/>
       <c r="B22" s="37"/>
       <c r="C22" s="5"/>
@@ -10081,7 +10122,7 @@
       <c r="E22" s="37"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:6">
       <c r="A23" s="37"/>
       <c r="B23" s="37"/>
       <c r="C23" s="5"/>
@@ -10089,7 +10130,7 @@
       <c r="E23" s="37"/>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:6">
       <c r="A24" s="37"/>
       <c r="B24" s="37"/>
       <c r="C24" s="5"/>
@@ -10097,7 +10138,7 @@
       <c r="E24" s="37"/>
       <c r="F24" s="5"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:6">
       <c r="A25" s="37"/>
       <c r="B25" s="37"/>
       <c r="C25" s="5"/>
@@ -10105,7 +10146,7 @@
       <c r="E25" s="37"/>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:6">
       <c r="A26" s="37"/>
       <c r="B26" s="37"/>
       <c r="C26" s="5"/>
@@ -10113,7 +10154,7 @@
       <c r="E26" s="37"/>
       <c r="F26" s="5"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:6">
       <c r="A27" s="37"/>
       <c r="B27" s="37"/>
       <c r="C27" s="5"/>
@@ -10121,7 +10162,7 @@
       <c r="E27" s="37"/>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:6">
       <c r="A28" s="37"/>
       <c r="B28" s="37"/>
       <c r="C28" s="5"/>
@@ -10129,7 +10170,7 @@
       <c r="E28" s="37"/>
       <c r="F28" s="5"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:6">
       <c r="A29" s="37"/>
       <c r="B29" s="37"/>
       <c r="C29" s="5"/>
@@ -10137,7 +10178,7 @@
       <c r="E29" s="37"/>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:6">
       <c r="A30" s="37"/>
       <c r="B30" s="37"/>
       <c r="C30" s="5"/>
@@ -10145,7 +10186,7 @@
       <c r="E30" s="37"/>
       <c r="F30" s="5"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:6">
       <c r="A31" s="37"/>
       <c r="B31" s="37"/>
       <c r="C31" s="5"/>
@@ -10153,7 +10194,7 @@
       <c r="E31" s="37"/>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:6">
       <c r="A32" s="37"/>
       <c r="B32" s="37"/>
       <c r="C32" s="5"/>
@@ -11520,14 +11561,6 @@
       <c r="D202" s="5"/>
       <c r="E202" s="37"/>
       <c r="F202" s="5"/>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203" s="37"/>
-      <c r="B203" s="37"/>
-      <c r="C203" s="5"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="37"/>
-      <c r="F203" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -11540,6 +11573,10 @@
     <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D6" r:id="rId1" xr:uid="{E0D9AA3D-ED3E-474C-8BB7-59191513ADE6}"/>
+    <hyperlink ref="D7" r:id="rId2" xr:uid="{D47B4A75-6145-064A-B334-6C22DEE8334B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/paper_list.xlsx
+++ b/src/paper_list.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yizhang/Desktop/Data Agents Survey/awesome-data-agents/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E48A0C-52E7-8B40-8E73-2E0BB8420B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43D8442-FBD6-BB48-83FF-2A3FA5FAB5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="46080" windowHeight="25420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="46080" windowHeight="25420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="L1" sheetId="1" r:id="rId1"/>
     <sheet name="L2" sheetId="2" r:id="rId2"/>
     <sheet name="L3" sheetId="3" r:id="rId3"/>
     <sheet name="survey" sheetId="4" r:id="rId4"/>
+    <sheet name="bench" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="532">
   <si>
     <t>Category</t>
   </si>
@@ -2578,6 +2579,70 @@
   <si>
     <t>https://arxiv.org/pdf/2508.05002v2</t>
     <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataSpace: Benchmarking Data Agents for Verifiable Analytics over Heterogeneous Workspaces</t>
+  </si>
+  <si>
+    <t>ArXiv</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2608.03451</t>
+  </si>
+  <si>
+    <t>AgenticDataBench: A Comprehensive Benchmark for Data Agents</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2607.01647</t>
+  </si>
+  <si>
+    <t>DABstep: Data Agent Benchmark for Multi-step Reasoning</t>
+  </si>
+  <si>
+    <t>ICML</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2606.15300</t>
+  </si>
+  <si>
+    <t>CoDA-Bench: Can Code Agents Handle Data-Intensive Tasks?</t>
+  </si>
+  <si>
+    <t>FDABench: A Benchmark for Data Agents on Analytical Queries over Heterogeneous Data</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2509.02473</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://arxiv.org/pdf/2506.23719</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>DAComp: Benchmarking Data Agents across the Full Data Intelligence Lifecycle</t>
+  </si>
+  <si>
+    <t>ICLR</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2512.04324</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can AI Agents Answer Your Data Questions? A Benchmark for Data Agents</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2603.20576</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>KramaBench: A Benchmark for AI Systems on Data-to-Insight Pipelines over Data Lakes</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2506.06541</t>
   </si>
 </sst>
 </file>
@@ -3476,7 +3541,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3795,9 +3860,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3805,6 +3867,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7544,7 +7615,7 @@
     </row>
     <row r="44" spans="1:8" ht="25.25" customHeight="1">
       <c r="A44" s="84"/>
-      <c r="B44" s="107"/>
+      <c r="B44" s="106"/>
       <c r="C44" s="65" t="s">
         <v>342</v>
       </c>
@@ -7564,13 +7635,13 @@
     <row r="45" spans="1:8" ht="25.25" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="10"/>
-      <c r="C45" s="108" t="s">
+      <c r="C45" s="107" t="s">
         <v>503</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="E45" s="109" t="s">
+      <c r="E45" s="108" t="s">
         <v>505</v>
       </c>
       <c r="F45" s="36" t="s">
@@ -9751,36 +9822,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="106" t="s">
+      <c r="C1" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="E1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="106" t="s">
+      <c r="F1" s="109" t="s">
         <v>415</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="G1" s="109" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="25.25" customHeight="1">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
+      <c r="A2" s="109"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="37">
@@ -11820,4 +11891,179 @@
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D3E3FEC-DF0F-2541-9F0A-5331A96D743D}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="13.3984375" customWidth="1"/>
+    <col min="2" max="2" width="52.19921875" customWidth="1"/>
+    <col min="3" max="3" width="38.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="81" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="81" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="81" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="81" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="82">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="82" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" s="83" t="s">
+        <v>515</v>
+      </c>
+      <c r="D2" s="82" t="s">
+        <v>514</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="82">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C3" s="83" t="s">
+        <v>517</v>
+      </c>
+      <c r="D3" s="82" t="s">
+        <v>514</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="82">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="s">
+        <v>528</v>
+      </c>
+      <c r="C4" s="104" t="s">
+        <v>529</v>
+      </c>
+      <c r="D4" s="82" t="s">
+        <v>514</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="82">
+        <v>2026</v>
+      </c>
+      <c r="B5" t="s">
+        <v>521</v>
+      </c>
+      <c r="C5" s="110" t="s">
+        <v>520</v>
+      </c>
+      <c r="D5" s="71" t="s">
+        <v>519</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="82">
+        <v>2026</v>
+      </c>
+      <c r="B6" t="s">
+        <v>522</v>
+      </c>
+      <c r="C6" s="110" t="s">
+        <v>523</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>510</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="111">
+        <v>2026</v>
+      </c>
+      <c r="B7" t="s">
+        <v>525</v>
+      </c>
+      <c r="C7" s="110" t="s">
+        <v>527</v>
+      </c>
+      <c r="D7" s="71" t="s">
+        <v>526</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="111">
+        <v>2026</v>
+      </c>
+      <c r="B8" t="s">
+        <v>530</v>
+      </c>
+      <c r="C8" s="110" t="s">
+        <v>531</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>526</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="82">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="s">
+        <v>518</v>
+      </c>
+      <c r="C9" s="110" t="s">
+        <v>524</v>
+      </c>
+      <c r="D9" s="82" t="s">
+        <v>514</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C6" r:id="rId1" xr:uid="{053DDF06-1361-AD41-B096-0870BBCDDF57}"/>
+    <hyperlink ref="C9" r:id="rId2" xr:uid="{2C147D96-0D84-D44C-AAF6-927707DB6BA4}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{2B6D77A6-1260-6D4A-B44F-D66489DEA31E}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{FC423275-9CAB-DE4E-ABBA-C9CF1A4EBFF4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>